--- a/Kooco_TexasHoldem/Assets/Resources/Language/Language.xlsx
+++ b/Kooco_TexasHoldem/Assets/Resources/Language/Language.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="PDWKAWSnmlKWwaDnRHdE9Bi2xns3vpiH0lYkRCmMyV8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6nwFSWNpi/8+ZnVlufCd3XzagaYjcSTTz10voUWY7qw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="392">
   <si>
     <t>ID</t>
   </si>
@@ -415,6 +415,12 @@
   </si>
   <si>
     <t>錯誤的邀請碼。</t>
+  </si>
+  <si>
+    <t>Duplicate Login.</t>
+  </si>
+  <si>
+    <t>帳號已登入。</t>
   </si>
   <si>
     <t>登入(LoginView)</t>
@@ -4135,9 +4141,15 @@
       <c r="Z73" s="5"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
+      <c r="A74" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
@@ -4163,77 +4175,71 @@
       <c r="Z74" s="5"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" s="2"/>
-      <c r="Q75" s="2"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="2"/>
-      <c r="T75" s="2"/>
-      <c r="U75" s="2"/>
-      <c r="V75" s="2"/>
-      <c r="W75" s="2"/>
-      <c r="X75" s="2"/>
-      <c r="Y75" s="2"/>
-      <c r="Z75" s="2"/>
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+      <c r="Q75" s="5"/>
+      <c r="R75" s="5"/>
+      <c r="S75" s="5"/>
+      <c r="T75" s="5"/>
+      <c r="U75" s="5"/>
+      <c r="V75" s="5"/>
+      <c r="W75" s="5"/>
+      <c r="X75" s="5"/>
+      <c r="Y75" s="5"/>
+      <c r="Z75" s="5"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C76" s="3" t="s">
+      <c r="A76" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-      <c r="I76" s="5"/>
-      <c r="J76" s="5"/>
-      <c r="K76" s="5"/>
-      <c r="L76" s="5"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="5"/>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="5"/>
-      <c r="R76" s="5"/>
-      <c r="S76" s="5"/>
-      <c r="T76" s="5"/>
-      <c r="U76" s="5"/>
-      <c r="V76" s="5"/>
-      <c r="W76" s="5"/>
-      <c r="X76" s="5"/>
-      <c r="Y76" s="5"/>
-      <c r="Z76" s="5"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="2"/>
+      <c r="S76" s="2"/>
+      <c r="T76" s="2"/>
+      <c r="U76" s="2"/>
+      <c r="V76" s="2"/>
+      <c r="W76" s="2"/>
+      <c r="X76" s="2"/>
+      <c r="Y76" s="2"/>
+      <c r="Z76" s="2"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D77" s="5"/>
@@ -4264,7 +4270,7 @@
       <c r="A78" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="5" t="s">
         <v>138</v>
       </c>
       <c r="C78" s="5" t="s">
@@ -4298,11 +4304,11 @@
       <c r="A79" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
@@ -4330,7 +4336,7 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>143</v>
@@ -4366,7 +4372,7 @@
       <c r="A81" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B81" s="28" t="s">
+      <c r="B81" s="5" t="s">
         <v>145</v>
       </c>
       <c r="C81" s="5" t="s">
@@ -4400,7 +4406,7 @@
       <c r="A82" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="28" t="s">
         <v>147</v>
       </c>
       <c r="C82" s="5" t="s">
@@ -4465,7 +4471,7 @@
       <c r="Z83" s="5"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="5" t="s">
         <v>151</v>
       </c>
       <c r="B84" s="5" t="s">
@@ -4567,7 +4573,7 @@
       <c r="Z86" s="5"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="5" t="s">
+      <c r="A87" s="6" t="s">
         <v>157</v>
       </c>
       <c r="B87" s="5" t="s">
@@ -4601,7 +4607,7 @@
       <c r="Z87" s="5"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="5" t="s">
         <v>159</v>
       </c>
       <c r="B88" s="5" t="s">
@@ -4635,7 +4641,7 @@
       <c r="Z88" s="5"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="5" t="s">
+      <c r="A89" s="6" t="s">
         <v>161</v>
       </c>
       <c r="B89" s="5" t="s">
@@ -4737,130 +4743,130 @@
       <c r="Z91" s="5"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
-      <c r="K92" s="1"/>
-      <c r="L92" s="1"/>
-      <c r="M92" s="1"/>
-      <c r="N92" s="1"/>
-      <c r="O92" s="1"/>
-      <c r="P92" s="1"/>
-      <c r="Q92" s="1"/>
-      <c r="R92" s="1"/>
-      <c r="S92" s="1"/>
-      <c r="T92" s="1"/>
-      <c r="U92" s="1"/>
-      <c r="V92" s="1"/>
-      <c r="W92" s="1"/>
-      <c r="X92" s="1"/>
-      <c r="Y92" s="1"/>
-      <c r="Z92" s="1"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5"/>
+      <c r="P92" s="5"/>
+      <c r="Q92" s="5"/>
+      <c r="R92" s="5"/>
+      <c r="S92" s="5"/>
+      <c r="T92" s="5"/>
+      <c r="U92" s="5"/>
+      <c r="V92" s="5"/>
+      <c r="W92" s="5"/>
+      <c r="X92" s="5"/>
+      <c r="Y92" s="5"/>
+      <c r="Z92" s="5"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
-      <c r="I93" s="5"/>
-      <c r="J93" s="5"/>
-      <c r="K93" s="5"/>
-      <c r="L93" s="5"/>
-      <c r="M93" s="5"/>
-      <c r="N93" s="5"/>
-      <c r="O93" s="5"/>
-      <c r="P93" s="5"/>
-      <c r="Q93" s="5"/>
-      <c r="R93" s="5"/>
-      <c r="S93" s="5"/>
-      <c r="T93" s="5"/>
-      <c r="U93" s="5"/>
-      <c r="V93" s="5"/>
-      <c r="W93" s="5"/>
-      <c r="X93" s="5"/>
-      <c r="Y93" s="5"/>
-      <c r="Z93" s="5"/>
+      <c r="A93" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+      <c r="N93" s="1"/>
+      <c r="O93" s="1"/>
+      <c r="P93" s="1"/>
+      <c r="Q93" s="1"/>
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
+      <c r="T93" s="1"/>
+      <c r="U93" s="1"/>
+      <c r="V93" s="1"/>
+      <c r="W93" s="1"/>
+      <c r="X93" s="1"/>
+      <c r="Y93" s="1"/>
+      <c r="Z93" s="1"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="B94" s="29"/>
-      <c r="C94" s="29"/>
-      <c r="D94" s="29"/>
-      <c r="E94" s="29"/>
-      <c r="F94" s="29"/>
-      <c r="G94" s="29"/>
-      <c r="H94" s="29"/>
-      <c r="I94" s="29"/>
-      <c r="J94" s="29"/>
-      <c r="K94" s="29"/>
-      <c r="L94" s="29"/>
-      <c r="M94" s="29"/>
-      <c r="N94" s="29"/>
-      <c r="O94" s="29"/>
-      <c r="P94" s="29"/>
-      <c r="Q94" s="29"/>
-      <c r="R94" s="29"/>
-      <c r="S94" s="29"/>
-      <c r="T94" s="29"/>
-      <c r="U94" s="29"/>
-      <c r="V94" s="29"/>
-      <c r="W94" s="29"/>
-      <c r="X94" s="29"/>
-      <c r="Y94" s="29"/>
-      <c r="Z94" s="29"/>
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="5"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="5"/>
+      <c r="P94" s="5"/>
+      <c r="Q94" s="5"/>
+      <c r="R94" s="5"/>
+      <c r="S94" s="5"/>
+      <c r="T94" s="5"/>
+      <c r="U94" s="5"/>
+      <c r="V94" s="5"/>
+      <c r="W94" s="5"/>
+      <c r="X94" s="5"/>
+      <c r="Y94" s="5"/>
+      <c r="Z94" s="5"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C95" s="5" t="s">
+      <c r="A95" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
-      <c r="H95" s="5"/>
-      <c r="I95" s="5"/>
-      <c r="J95" s="5"/>
-      <c r="K95" s="5"/>
-      <c r="L95" s="5"/>
-      <c r="M95" s="5"/>
-      <c r="N95" s="5"/>
-      <c r="O95" s="5"/>
-      <c r="P95" s="5"/>
-      <c r="Q95" s="5"/>
-      <c r="R95" s="5"/>
-      <c r="S95" s="5"/>
-      <c r="T95" s="5"/>
-      <c r="U95" s="5"/>
-      <c r="V95" s="5"/>
-      <c r="W95" s="5"/>
-      <c r="X95" s="5"/>
-      <c r="Y95" s="5"/>
-      <c r="Z95" s="5"/>
+      <c r="B95" s="29"/>
+      <c r="C95" s="29"/>
+      <c r="D95" s="29"/>
+      <c r="E95" s="29"/>
+      <c r="F95" s="29"/>
+      <c r="G95" s="29"/>
+      <c r="H95" s="29"/>
+      <c r="I95" s="29"/>
+      <c r="J95" s="29"/>
+      <c r="K95" s="29"/>
+      <c r="L95" s="29"/>
+      <c r="M95" s="29"/>
+      <c r="N95" s="29"/>
+      <c r="O95" s="29"/>
+      <c r="P95" s="29"/>
+      <c r="Q95" s="29"/>
+      <c r="R95" s="29"/>
+      <c r="S95" s="29"/>
+      <c r="T95" s="29"/>
+      <c r="U95" s="29"/>
+      <c r="V95" s="29"/>
+      <c r="W95" s="29"/>
+      <c r="X95" s="29"/>
+      <c r="Y95" s="29"/>
+      <c r="Z95" s="29"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="5" t="s">
@@ -4903,7 +4909,7 @@
       <c r="B97" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C97" s="6" t="s">
+      <c r="C97" s="5" t="s">
         <v>175</v>
       </c>
       <c r="D97" s="5"/>
@@ -4931,68 +4937,68 @@
       <c r="Z97" s="5"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="29" t="s">
+      <c r="A98" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B98" s="29"/>
-      <c r="C98" s="29"/>
-      <c r="D98" s="29"/>
-      <c r="E98" s="29"/>
-      <c r="F98" s="29"/>
-      <c r="G98" s="29"/>
-      <c r="H98" s="29"/>
-      <c r="I98" s="29"/>
-      <c r="J98" s="29"/>
-      <c r="K98" s="29"/>
-      <c r="L98" s="29"/>
-      <c r="M98" s="29"/>
-      <c r="N98" s="29"/>
-      <c r="O98" s="29"/>
-      <c r="P98" s="29"/>
-      <c r="Q98" s="29"/>
-      <c r="R98" s="29"/>
-      <c r="S98" s="29"/>
-      <c r="T98" s="29"/>
-      <c r="U98" s="29"/>
-      <c r="V98" s="29"/>
-      <c r="W98" s="29"/>
-      <c r="X98" s="29"/>
-      <c r="Y98" s="29"/>
-      <c r="Z98" s="29"/>
+      <c r="B98" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="5"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5"/>
+      <c r="O98" s="5"/>
+      <c r="P98" s="5"/>
+      <c r="Q98" s="5"/>
+      <c r="R98" s="5"/>
+      <c r="S98" s="5"/>
+      <c r="T98" s="5"/>
+      <c r="U98" s="5"/>
+      <c r="V98" s="5"/>
+      <c r="W98" s="5"/>
+      <c r="X98" s="5"/>
+      <c r="Y98" s="5"/>
+      <c r="Z98" s="5"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C99" s="5" t="s">
+      <c r="A99" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="5"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="5"/>
-      <c r="K99" s="5"/>
-      <c r="L99" s="5"/>
-      <c r="M99" s="5"/>
-      <c r="N99" s="5"/>
-      <c r="O99" s="5"/>
-      <c r="P99" s="5"/>
-      <c r="Q99" s="5"/>
-      <c r="R99" s="5"/>
-      <c r="S99" s="5"/>
-      <c r="T99" s="5"/>
-      <c r="U99" s="5"/>
-      <c r="V99" s="5"/>
-      <c r="W99" s="5"/>
-      <c r="X99" s="5"/>
-      <c r="Y99" s="5"/>
-      <c r="Z99" s="5"/>
+      <c r="B99" s="29"/>
+      <c r="C99" s="29"/>
+      <c r="D99" s="29"/>
+      <c r="E99" s="29"/>
+      <c r="F99" s="29"/>
+      <c r="G99" s="29"/>
+      <c r="H99" s="29"/>
+      <c r="I99" s="29"/>
+      <c r="J99" s="29"/>
+      <c r="K99" s="29"/>
+      <c r="L99" s="29"/>
+      <c r="M99" s="29"/>
+      <c r="N99" s="29"/>
+      <c r="O99" s="29"/>
+      <c r="P99" s="29"/>
+      <c r="Q99" s="29"/>
+      <c r="R99" s="29"/>
+      <c r="S99" s="29"/>
+      <c r="T99" s="29"/>
+      <c r="U99" s="29"/>
+      <c r="V99" s="29"/>
+      <c r="W99" s="29"/>
+      <c r="X99" s="29"/>
+      <c r="Y99" s="29"/>
+      <c r="Z99" s="29"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="5" t="s">
@@ -5097,132 +5103,132 @@
       <c r="Z102" s="5"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="30" t="s">
+      <c r="A103" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B103" s="30"/>
-      <c r="C103" s="30"/>
-      <c r="D103" s="30"/>
-      <c r="E103" s="30"/>
-      <c r="F103" s="30"/>
-      <c r="G103" s="30"/>
-      <c r="H103" s="30"/>
-      <c r="I103" s="30"/>
-      <c r="J103" s="30"/>
-      <c r="K103" s="30"/>
-      <c r="L103" s="30"/>
-      <c r="M103" s="30"/>
-      <c r="N103" s="30"/>
-      <c r="O103" s="30"/>
-      <c r="P103" s="30"/>
-      <c r="Q103" s="30"/>
-      <c r="R103" s="30"/>
-      <c r="S103" s="30"/>
-      <c r="T103" s="30"/>
-      <c r="U103" s="30"/>
-      <c r="V103" s="30"/>
-      <c r="W103" s="30"/>
-      <c r="X103" s="30"/>
-      <c r="Y103" s="30"/>
-      <c r="Z103" s="30"/>
+      <c r="B103" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="5"/>
+      <c r="K103" s="5"/>
+      <c r="L103" s="5"/>
+      <c r="M103" s="5"/>
+      <c r="N103" s="5"/>
+      <c r="O103" s="5"/>
+      <c r="P103" s="5"/>
+      <c r="Q103" s="5"/>
+      <c r="R103" s="5"/>
+      <c r="S103" s="5"/>
+      <c r="T103" s="5"/>
+      <c r="U103" s="5"/>
+      <c r="V103" s="5"/>
+      <c r="W103" s="5"/>
+      <c r="X103" s="5"/>
+      <c r="Y103" s="5"/>
+      <c r="Z103" s="5"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="5"/>
-      <c r="K104" s="5"/>
-      <c r="L104" s="5"/>
-      <c r="M104" s="5"/>
-      <c r="N104" s="5"/>
-      <c r="O104" s="5"/>
-      <c r="P104" s="5"/>
-      <c r="Q104" s="5"/>
-      <c r="R104" s="5"/>
-      <c r="S104" s="5"/>
-      <c r="T104" s="5"/>
-      <c r="U104" s="5"/>
-      <c r="V104" s="5"/>
-      <c r="W104" s="5"/>
-      <c r="X104" s="5"/>
-      <c r="Y104" s="5"/>
-      <c r="Z104" s="5"/>
+      <c r="A104" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="B104" s="30"/>
+      <c r="C104" s="30"/>
+      <c r="D104" s="30"/>
+      <c r="E104" s="30"/>
+      <c r="F104" s="30"/>
+      <c r="G104" s="30"/>
+      <c r="H104" s="30"/>
+      <c r="I104" s="30"/>
+      <c r="J104" s="30"/>
+      <c r="K104" s="30"/>
+      <c r="L104" s="30"/>
+      <c r="M104" s="30"/>
+      <c r="N104" s="30"/>
+      <c r="O104" s="30"/>
+      <c r="P104" s="30"/>
+      <c r="Q104" s="30"/>
+      <c r="R104" s="30"/>
+      <c r="S104" s="30"/>
+      <c r="T104" s="30"/>
+      <c r="U104" s="30"/>
+      <c r="V104" s="30"/>
+      <c r="W104" s="30"/>
+      <c r="X104" s="30"/>
+      <c r="Y104" s="30"/>
+      <c r="Z104" s="30"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="29" t="s">
+      <c r="A105" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C105" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B105" s="29"/>
-      <c r="C105" s="29"/>
-      <c r="D105" s="29"/>
-      <c r="E105" s="29"/>
-      <c r="F105" s="29"/>
-      <c r="G105" s="29"/>
-      <c r="H105" s="29"/>
-      <c r="I105" s="29"/>
-      <c r="J105" s="29"/>
-      <c r="K105" s="29"/>
-      <c r="L105" s="29"/>
-      <c r="M105" s="29"/>
-      <c r="N105" s="29"/>
-      <c r="O105" s="29"/>
-      <c r="P105" s="29"/>
-      <c r="Q105" s="29"/>
-      <c r="R105" s="29"/>
-      <c r="S105" s="29"/>
-      <c r="T105" s="29"/>
-      <c r="U105" s="29"/>
-      <c r="V105" s="29"/>
-      <c r="W105" s="29"/>
-      <c r="X105" s="29"/>
-      <c r="Y105" s="29"/>
-      <c r="Z105" s="29"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5"/>
+      <c r="K105" s="5"/>
+      <c r="L105" s="5"/>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
+      <c r="O105" s="5"/>
+      <c r="P105" s="5"/>
+      <c r="Q105" s="5"/>
+      <c r="R105" s="5"/>
+      <c r="S105" s="5"/>
+      <c r="T105" s="5"/>
+      <c r="U105" s="5"/>
+      <c r="V105" s="5"/>
+      <c r="W105" s="5"/>
+      <c r="X105" s="5"/>
+      <c r="Y105" s="5"/>
+      <c r="Z105" s="5"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C106" s="5" t="s">
+      <c r="A106" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="5"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="5"/>
-      <c r="M106" s="5"/>
-      <c r="N106" s="5"/>
-      <c r="O106" s="5"/>
-      <c r="P106" s="5"/>
-      <c r="Q106" s="5"/>
-      <c r="R106" s="5"/>
-      <c r="S106" s="5"/>
-      <c r="T106" s="5"/>
-      <c r="U106" s="5"/>
-      <c r="V106" s="5"/>
-      <c r="W106" s="5"/>
-      <c r="X106" s="5"/>
-      <c r="Y106" s="5"/>
-      <c r="Z106" s="5"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
+      <c r="D106" s="29"/>
+      <c r="E106" s="29"/>
+      <c r="F106" s="29"/>
+      <c r="G106" s="29"/>
+      <c r="H106" s="29"/>
+      <c r="I106" s="29"/>
+      <c r="J106" s="29"/>
+      <c r="K106" s="29"/>
+      <c r="L106" s="29"/>
+      <c r="M106" s="29"/>
+      <c r="N106" s="29"/>
+      <c r="O106" s="29"/>
+      <c r="P106" s="29"/>
+      <c r="Q106" s="29"/>
+      <c r="R106" s="29"/>
+      <c r="S106" s="29"/>
+      <c r="T106" s="29"/>
+      <c r="U106" s="29"/>
+      <c r="V106" s="29"/>
+      <c r="W106" s="29"/>
+      <c r="X106" s="29"/>
+      <c r="Y106" s="29"/>
+      <c r="Z106" s="29"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="5" t="s">
@@ -5259,7 +5265,7 @@
       <c r="Z107" s="5"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="5" t="s">
         <v>192</v>
       </c>
       <c r="B108" s="5" t="s">
@@ -5293,302 +5299,302 @@
       <c r="Z108" s="5"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="29" t="s">
+      <c r="A109" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="B109" s="29"/>
-      <c r="C109" s="29"/>
-      <c r="D109" s="29"/>
-      <c r="E109" s="29"/>
-      <c r="F109" s="29"/>
-      <c r="G109" s="29"/>
-      <c r="H109" s="29"/>
-      <c r="I109" s="29"/>
-      <c r="J109" s="29"/>
-      <c r="K109" s="29"/>
-      <c r="L109" s="29"/>
-      <c r="M109" s="29"/>
-      <c r="N109" s="29"/>
-      <c r="O109" s="29"/>
-      <c r="P109" s="29"/>
-      <c r="Q109" s="29"/>
-      <c r="R109" s="29"/>
-      <c r="S109" s="29"/>
-      <c r="T109" s="29"/>
-      <c r="U109" s="29"/>
-      <c r="V109" s="29"/>
-      <c r="W109" s="29"/>
-      <c r="X109" s="29"/>
-      <c r="Y109" s="29"/>
-      <c r="Z109" s="29"/>
+      <c r="B109" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="5"/>
+      <c r="K109" s="5"/>
+      <c r="L109" s="5"/>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="5"/>
+      <c r="P109" s="5"/>
+      <c r="Q109" s="5"/>
+      <c r="R109" s="5"/>
+      <c r="S109" s="5"/>
+      <c r="T109" s="5"/>
+      <c r="U109" s="5"/>
+      <c r="V109" s="5"/>
+      <c r="W109" s="5"/>
+      <c r="X109" s="5"/>
+      <c r="Y109" s="5"/>
+      <c r="Z109" s="5"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C110" s="6" t="s">
+      <c r="A110" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="1"/>
-      <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="1"/>
-      <c r="K110" s="1"/>
-      <c r="L110" s="1"/>
-      <c r="M110" s="1"/>
-      <c r="N110" s="1"/>
-      <c r="O110" s="1"/>
-      <c r="P110" s="1"/>
-      <c r="Q110" s="1"/>
-      <c r="R110" s="1"/>
-      <c r="S110" s="1"/>
-      <c r="T110" s="1"/>
-      <c r="U110" s="1"/>
-      <c r="V110" s="1"/>
-      <c r="W110" s="1"/>
-      <c r="X110" s="1"/>
-      <c r="Y110" s="1"/>
-      <c r="Z110" s="1"/>
+      <c r="B110" s="29"/>
+      <c r="C110" s="29"/>
+      <c r="D110" s="29"/>
+      <c r="E110" s="29"/>
+      <c r="F110" s="29"/>
+      <c r="G110" s="29"/>
+      <c r="H110" s="29"/>
+      <c r="I110" s="29"/>
+      <c r="J110" s="29"/>
+      <c r="K110" s="29"/>
+      <c r="L110" s="29"/>
+      <c r="M110" s="29"/>
+      <c r="N110" s="29"/>
+      <c r="O110" s="29"/>
+      <c r="P110" s="29"/>
+      <c r="Q110" s="29"/>
+      <c r="R110" s="29"/>
+      <c r="S110" s="29"/>
+      <c r="T110" s="29"/>
+      <c r="U110" s="29"/>
+      <c r="V110" s="29"/>
+      <c r="W110" s="29"/>
+      <c r="X110" s="29"/>
+      <c r="Y110" s="29"/>
+      <c r="Z110" s="29"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="31" t="s">
+      <c r="A111" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B111" s="32"/>
-      <c r="C111" s="29"/>
-      <c r="D111" s="32"/>
-      <c r="E111" s="32"/>
-      <c r="F111" s="32"/>
-      <c r="G111" s="32"/>
-      <c r="H111" s="32"/>
-      <c r="I111" s="32"/>
-      <c r="J111" s="32"/>
-      <c r="K111" s="32"/>
-      <c r="L111" s="32"/>
-      <c r="M111" s="32"/>
-      <c r="N111" s="32"/>
-      <c r="O111" s="32"/>
-      <c r="P111" s="32"/>
-      <c r="Q111" s="32"/>
-      <c r="R111" s="32"/>
-      <c r="S111" s="32"/>
-      <c r="T111" s="32"/>
-      <c r="U111" s="32"/>
-      <c r="V111" s="32"/>
-      <c r="W111" s="32"/>
-      <c r="X111" s="32"/>
-      <c r="Y111" s="32"/>
-      <c r="Z111" s="32"/>
+      <c r="B111" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="M111" s="1"/>
+      <c r="N111" s="1"/>
+      <c r="O111" s="1"/>
+      <c r="P111" s="1"/>
+      <c r="Q111" s="1"/>
+      <c r="R111" s="1"/>
+      <c r="S111" s="1"/>
+      <c r="T111" s="1"/>
+      <c r="U111" s="1"/>
+      <c r="V111" s="1"/>
+      <c r="W111" s="1"/>
+      <c r="X111" s="1"/>
+      <c r="Y111" s="1"/>
+      <c r="Z111" s="1"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C112" s="6" t="s">
+      <c r="A112" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
-      <c r="G112" s="5"/>
-      <c r="H112" s="5"/>
-      <c r="I112" s="5"/>
-      <c r="J112" s="5"/>
-      <c r="K112" s="5"/>
-      <c r="L112" s="5"/>
-      <c r="M112" s="5"/>
-      <c r="N112" s="5"/>
-      <c r="O112" s="5"/>
-      <c r="P112" s="5"/>
-      <c r="Q112" s="5"/>
-      <c r="R112" s="5"/>
-      <c r="S112" s="5"/>
-      <c r="T112" s="5"/>
-      <c r="U112" s="5"/>
-      <c r="V112" s="5"/>
-      <c r="W112" s="5"/>
-      <c r="X112" s="5"/>
-      <c r="Y112" s="5"/>
-      <c r="Z112" s="5"/>
+      <c r="B112" s="32"/>
+      <c r="C112" s="29"/>
+      <c r="D112" s="32"/>
+      <c r="E112" s="32"/>
+      <c r="F112" s="32"/>
+      <c r="G112" s="32"/>
+      <c r="H112" s="32"/>
+      <c r="I112" s="32"/>
+      <c r="J112" s="32"/>
+      <c r="K112" s="32"/>
+      <c r="L112" s="32"/>
+      <c r="M112" s="32"/>
+      <c r="N112" s="32"/>
+      <c r="O112" s="32"/>
+      <c r="P112" s="32"/>
+      <c r="Q112" s="32"/>
+      <c r="R112" s="32"/>
+      <c r="S112" s="32"/>
+      <c r="T112" s="32"/>
+      <c r="U112" s="32"/>
+      <c r="V112" s="32"/>
+      <c r="W112" s="32"/>
+      <c r="X112" s="32"/>
+      <c r="Y112" s="32"/>
+      <c r="Z112" s="32"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="17" t="s">
+      <c r="A113" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="B113" s="17" t="s">
+      <c r="B113" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C113" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="D113" s="33"/>
-      <c r="E113" s="33"/>
-      <c r="F113" s="33"/>
-      <c r="G113" s="33"/>
-      <c r="H113" s="33"/>
-      <c r="I113" s="33"/>
-      <c r="J113" s="33"/>
-      <c r="K113" s="33"/>
-      <c r="L113" s="33"/>
-      <c r="M113" s="33"/>
-      <c r="N113" s="33"/>
-      <c r="O113" s="33"/>
-      <c r="P113" s="33"/>
-      <c r="Q113" s="33"/>
-      <c r="R113" s="33"/>
-      <c r="S113" s="33"/>
-      <c r="T113" s="33"/>
-      <c r="U113" s="33"/>
-      <c r="V113" s="33"/>
-      <c r="W113" s="33"/>
-      <c r="X113" s="33"/>
-      <c r="Y113" s="33"/>
-      <c r="Z113" s="33"/>
+      <c r="C113" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D113" s="5"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="5"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="5"/>
+      <c r="I113" s="5"/>
+      <c r="J113" s="5"/>
+      <c r="K113" s="5"/>
+      <c r="L113" s="5"/>
+      <c r="M113" s="5"/>
+      <c r="N113" s="5"/>
+      <c r="O113" s="5"/>
+      <c r="P113" s="5"/>
+      <c r="Q113" s="5"/>
+      <c r="R113" s="5"/>
+      <c r="S113" s="5"/>
+      <c r="T113" s="5"/>
+      <c r="U113" s="5"/>
+      <c r="V113" s="5"/>
+      <c r="W113" s="5"/>
+      <c r="X113" s="5"/>
+      <c r="Y113" s="5"/>
+      <c r="Z113" s="5"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="C114" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
-      <c r="H114" s="5"/>
-      <c r="I114" s="5"/>
-      <c r="J114" s="5"/>
-      <c r="K114" s="5"/>
-      <c r="L114" s="5"/>
-      <c r="M114" s="5"/>
-      <c r="N114" s="5"/>
-      <c r="O114" s="5"/>
-      <c r="P114" s="5"/>
-      <c r="Q114" s="5"/>
-      <c r="R114" s="5"/>
-      <c r="S114" s="5"/>
-      <c r="T114" s="5"/>
-      <c r="U114" s="5"/>
-      <c r="V114" s="5"/>
-      <c r="W114" s="5"/>
-      <c r="X114" s="5"/>
-      <c r="Y114" s="5"/>
-      <c r="Z114" s="5"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="21"/>
-      <c r="B115" s="21"/>
-      <c r="C115" s="21"/>
-      <c r="D115" s="21"/>
-      <c r="E115" s="21"/>
-      <c r="F115" s="21"/>
-      <c r="G115" s="21"/>
-      <c r="H115" s="21"/>
-      <c r="I115" s="21"/>
-      <c r="J115" s="21"/>
-      <c r="K115" s="21"/>
-      <c r="L115" s="21"/>
-      <c r="M115" s="21"/>
-      <c r="N115" s="21"/>
-      <c r="O115" s="21"/>
-      <c r="P115" s="21"/>
-      <c r="Q115" s="21"/>
-      <c r="R115" s="21"/>
-      <c r="S115" s="21"/>
-      <c r="T115" s="21"/>
-      <c r="U115" s="21"/>
-      <c r="V115" s="21"/>
-      <c r="W115" s="21"/>
-      <c r="X115" s="21"/>
-      <c r="Y115" s="21"/>
-      <c r="Z115" s="21"/>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="2" t="s">
+      <c r="C114" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D114" s="33"/>
+      <c r="E114" s="33"/>
+      <c r="F114" s="33"/>
+      <c r="G114" s="33"/>
+      <c r="H114" s="33"/>
+      <c r="I114" s="33"/>
+      <c r="J114" s="33"/>
+      <c r="K114" s="33"/>
+      <c r="L114" s="33"/>
+      <c r="M114" s="33"/>
+      <c r="N114" s="33"/>
+      <c r="O114" s="33"/>
+      <c r="P114" s="33"/>
+      <c r="Q114" s="33"/>
+      <c r="R114" s="33"/>
+      <c r="S114" s="33"/>
+      <c r="T114" s="33"/>
+      <c r="U114" s="33"/>
+      <c r="V114" s="33"/>
+      <c r="W114" s="33"/>
+      <c r="X114" s="33"/>
+      <c r="Y114" s="33"/>
+      <c r="Z114" s="33"/>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2"/>
-      <c r="J116" s="2"/>
-      <c r="K116" s="2"/>
-      <c r="L116" s="2"/>
-      <c r="M116" s="2"/>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" s="2"/>
-      <c r="Q116" s="2"/>
-      <c r="R116" s="2"/>
-      <c r="S116" s="2"/>
-      <c r="T116" s="2"/>
-      <c r="U116" s="2"/>
-      <c r="V116" s="2"/>
-      <c r="W116" s="2"/>
-      <c r="X116" s="2"/>
-      <c r="Y116" s="2"/>
-      <c r="Z116" s="2"/>
+      <c r="B115" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D115" s="5"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="5"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="5"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="5"/>
+      <c r="K115" s="5"/>
+      <c r="L115" s="5"/>
+      <c r="M115" s="5"/>
+      <c r="N115" s="5"/>
+      <c r="O115" s="5"/>
+      <c r="P115" s="5"/>
+      <c r="Q115" s="5"/>
+      <c r="R115" s="5"/>
+      <c r="S115" s="5"/>
+      <c r="T115" s="5"/>
+      <c r="U115" s="5"/>
+      <c r="V115" s="5"/>
+      <c r="W115" s="5"/>
+      <c r="X115" s="5"/>
+      <c r="Y115" s="5"/>
+      <c r="Z115" s="5"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="21"/>
+      <c r="B116" s="21"/>
+      <c r="C116" s="21"/>
+      <c r="D116" s="21"/>
+      <c r="E116" s="21"/>
+      <c r="F116" s="21"/>
+      <c r="G116" s="21"/>
+      <c r="H116" s="21"/>
+      <c r="I116" s="21"/>
+      <c r="J116" s="21"/>
+      <c r="K116" s="21"/>
+      <c r="L116" s="21"/>
+      <c r="M116" s="21"/>
+      <c r="N116" s="21"/>
+      <c r="O116" s="21"/>
+      <c r="P116" s="21"/>
+      <c r="Q116" s="21"/>
+      <c r="R116" s="21"/>
+      <c r="S116" s="21"/>
+      <c r="T116" s="21"/>
+      <c r="U116" s="21"/>
+      <c r="V116" s="21"/>
+      <c r="W116" s="21"/>
+      <c r="X116" s="21"/>
+      <c r="Y116" s="21"/>
+      <c r="Z116" s="21"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
-      <c r="G117" s="5"/>
-      <c r="H117" s="5"/>
-      <c r="I117" s="5"/>
-      <c r="J117" s="5"/>
-      <c r="K117" s="5"/>
-      <c r="L117" s="5"/>
-      <c r="M117" s="5"/>
-      <c r="N117" s="5"/>
-      <c r="O117" s="5"/>
-      <c r="P117" s="5"/>
-      <c r="Q117" s="5"/>
-      <c r="R117" s="5"/>
-      <c r="S117" s="5"/>
-      <c r="T117" s="5"/>
-      <c r="U117" s="5"/>
-      <c r="V117" s="5"/>
-      <c r="W117" s="5"/>
-      <c r="X117" s="5"/>
-      <c r="Y117" s="5"/>
-      <c r="Z117" s="5"/>
+      <c r="A117" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
+      <c r="J117" s="2"/>
+      <c r="K117" s="2"/>
+      <c r="L117" s="2"/>
+      <c r="M117" s="2"/>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" s="2"/>
+      <c r="Q117" s="2"/>
+      <c r="R117" s="2"/>
+      <c r="S117" s="2"/>
+      <c r="T117" s="2"/>
+      <c r="U117" s="2"/>
+      <c r="V117" s="2"/>
+      <c r="W117" s="2"/>
+      <c r="X117" s="2"/>
+      <c r="Y117" s="2"/>
+      <c r="Z117" s="2"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>205</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
@@ -5649,9 +5655,15 @@
       <c r="Z119" s="5"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="5"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="5"/>
+      <c r="A120" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>210</v>
+      </c>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
@@ -5677,78 +5689,72 @@
       <c r="Z120" s="5"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-      <c r="H121" s="2"/>
-      <c r="I121" s="2"/>
-      <c r="J121" s="2"/>
-      <c r="K121" s="2"/>
-      <c r="L121" s="2"/>
-      <c r="M121" s="2"/>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" s="2"/>
-      <c r="Q121" s="2"/>
-      <c r="R121" s="2"/>
-      <c r="S121" s="2"/>
-      <c r="T121" s="2"/>
-      <c r="U121" s="2"/>
-      <c r="V121" s="2"/>
-      <c r="W121" s="2"/>
-      <c r="X121" s="2"/>
-      <c r="Y121" s="2"/>
-      <c r="Z121" s="2"/>
+      <c r="A121" s="5"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="5"/>
+      <c r="D121" s="5"/>
+      <c r="E121" s="5"/>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="5"/>
+      <c r="I121" s="5"/>
+      <c r="J121" s="5"/>
+      <c r="K121" s="5"/>
+      <c r="L121" s="5"/>
+      <c r="M121" s="5"/>
+      <c r="N121" s="5"/>
+      <c r="O121" s="5"/>
+      <c r="P121" s="5"/>
+      <c r="Q121" s="5"/>
+      <c r="R121" s="5"/>
+      <c r="S121" s="5"/>
+      <c r="T121" s="5"/>
+      <c r="U121" s="5"/>
+      <c r="V121" s="5"/>
+      <c r="W121" s="5"/>
+      <c r="X121" s="5"/>
+      <c r="Y121" s="5"/>
+      <c r="Z121" s="5"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="C122" s="1" t="s">
+      <c r="A122" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="1"/>
-      <c r="K122" s="1"/>
-      <c r="L122" s="1"/>
-      <c r="M122" s="1"/>
-      <c r="N122" s="1"/>
-      <c r="O122" s="1"/>
-      <c r="P122" s="1"/>
-      <c r="Q122" s="1"/>
-      <c r="R122" s="1"/>
-      <c r="S122" s="1"/>
-      <c r="T122" s="1"/>
-      <c r="U122" s="1"/>
-      <c r="V122" s="1"/>
-      <c r="W122" s="1"/>
-      <c r="X122" s="1"/>
-      <c r="Y122" s="1"/>
-      <c r="Z122" s="1"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="2"/>
+      <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
+      <c r="M122" s="2"/>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" s="2"/>
+      <c r="Q122" s="2"/>
+      <c r="R122" s="2"/>
+      <c r="S122" s="2"/>
+      <c r="T122" s="2"/>
+      <c r="U122" s="2"/>
+      <c r="V122" s="2"/>
+      <c r="W122" s="2"/>
+      <c r="X122" s="2"/>
+      <c r="Y122" s="2"/>
+      <c r="Z122" s="2"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="1" t="s">
         <v>212</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
@@ -5776,7 +5782,7 @@
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>215</v>
@@ -5911,9 +5917,15 @@
       <c r="Z127" s="1"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="1"/>
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
+      <c r="A128" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -5939,73 +5951,73 @@
       <c r="Z128" s="1"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
-      <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-      <c r="H129" s="2"/>
-      <c r="I129" s="2"/>
-      <c r="J129" s="2"/>
-      <c r="K129" s="2"/>
-      <c r="L129" s="2"/>
-      <c r="M129" s="2"/>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-      <c r="P129" s="2"/>
-      <c r="Q129" s="2"/>
-      <c r="R129" s="2"/>
-      <c r="S129" s="2"/>
-      <c r="T129" s="2"/>
-      <c r="U129" s="2"/>
-      <c r="V129" s="2"/>
-      <c r="W129" s="2"/>
-      <c r="X129" s="2"/>
-      <c r="Y129" s="2"/>
-      <c r="Z129" s="2"/>
+      <c r="A129" s="1"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="L129" s="1"/>
+      <c r="M129" s="1"/>
+      <c r="N129" s="1"/>
+      <c r="O129" s="1"/>
+      <c r="P129" s="1"/>
+      <c r="Q129" s="1"/>
+      <c r="R129" s="1"/>
+      <c r="S129" s="1"/>
+      <c r="T129" s="1"/>
+      <c r="U129" s="1"/>
+      <c r="V129" s="1"/>
+      <c r="W129" s="1"/>
+      <c r="X129" s="1"/>
+      <c r="Y129" s="1"/>
+      <c r="Z129" s="1"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="D130" s="1"/>
-      <c r="E130" s="1"/>
-      <c r="F130" s="1"/>
-      <c r="G130" s="1"/>
-      <c r="H130" s="1"/>
-      <c r="I130" s="1"/>
-      <c r="J130" s="1"/>
-      <c r="K130" s="1"/>
-      <c r="L130" s="1"/>
-      <c r="M130" s="1"/>
-      <c r="N130" s="1"/>
-      <c r="O130" s="1"/>
-      <c r="P130" s="1"/>
-      <c r="Q130" s="1"/>
-      <c r="R130" s="1"/>
-      <c r="S130" s="1"/>
-      <c r="T130" s="1"/>
-      <c r="U130" s="1"/>
-      <c r="V130" s="1"/>
-      <c r="W130" s="1"/>
-      <c r="X130" s="1"/>
-      <c r="Y130" s="1"/>
-      <c r="Z130" s="1"/>
+      <c r="A130" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="2"/>
+      <c r="H130" s="2"/>
+      <c r="I130" s="2"/>
+      <c r="J130" s="2"/>
+      <c r="K130" s="2"/>
+      <c r="L130" s="2"/>
+      <c r="M130" s="2"/>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" s="2"/>
+      <c r="Q130" s="2"/>
+      <c r="R130" s="2"/>
+      <c r="S130" s="2"/>
+      <c r="T130" s="2"/>
+      <c r="U130" s="2"/>
+      <c r="V130" s="2"/>
+      <c r="W130" s="2"/>
+      <c r="X130" s="2"/>
+      <c r="Y130" s="2"/>
+      <c r="Z130" s="2"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
+      <c r="A131" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
@@ -6031,68 +6043,62 @@
       <c r="Z131" s="1"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="1"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+      <c r="E132" s="1"/>
+      <c r="F132" s="1"/>
+      <c r="G132" s="1"/>
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+      <c r="J132" s="1"/>
+      <c r="K132" s="1"/>
+      <c r="L132" s="1"/>
+      <c r="M132" s="1"/>
+      <c r="N132" s="1"/>
+      <c r="O132" s="1"/>
+      <c r="P132" s="1"/>
+      <c r="Q132" s="1"/>
+      <c r="R132" s="1"/>
+      <c r="S132" s="1"/>
+      <c r="T132" s="1"/>
+      <c r="U132" s="1"/>
+      <c r="V132" s="1"/>
+      <c r="W132" s="1"/>
+      <c r="X132" s="1"/>
+      <c r="Y132" s="1"/>
+      <c r="Z132" s="1"/>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-      <c r="H132" s="2"/>
-      <c r="I132" s="2"/>
-      <c r="J132" s="2"/>
-      <c r="K132" s="2"/>
-      <c r="L132" s="2"/>
-      <c r="M132" s="2"/>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
-      <c r="P132" s="2"/>
-      <c r="Q132" s="2"/>
-      <c r="R132" s="2"/>
-      <c r="S132" s="2"/>
-      <c r="T132" s="2"/>
-      <c r="U132" s="2"/>
-      <c r="V132" s="2"/>
-      <c r="W132" s="2"/>
-      <c r="X132" s="2"/>
-      <c r="Y132" s="2"/>
-      <c r="Z132" s="2"/>
-    </row>
-    <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="D133" s="1"/>
-      <c r="E133" s="1"/>
-      <c r="F133" s="1"/>
-      <c r="G133" s="1"/>
-      <c r="H133" s="1"/>
-      <c r="I133" s="1"/>
-      <c r="J133" s="1"/>
-      <c r="K133" s="1"/>
-      <c r="L133" s="1"/>
-      <c r="M133" s="1"/>
-      <c r="N133" s="1"/>
-      <c r="O133" s="1"/>
-      <c r="P133" s="1"/>
-      <c r="Q133" s="1"/>
-      <c r="R133" s="1"/>
-      <c r="S133" s="1"/>
-      <c r="T133" s="1"/>
-      <c r="U133" s="1"/>
-      <c r="V133" s="1"/>
-      <c r="W133" s="1"/>
-      <c r="X133" s="1"/>
-      <c r="Y133" s="1"/>
-      <c r="Z133" s="1"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+      <c r="I133" s="2"/>
+      <c r="J133" s="2"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
+      <c r="M133" s="2"/>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" s="2"/>
+      <c r="Q133" s="2"/>
+      <c r="R133" s="2"/>
+      <c r="S133" s="2"/>
+      <c r="T133" s="2"/>
+      <c r="U133" s="2"/>
+      <c r="V133" s="2"/>
+      <c r="W133" s="2"/>
+      <c r="X133" s="2"/>
+      <c r="Y133" s="2"/>
+      <c r="Z133" s="2"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="1" t="s">
@@ -6163,174 +6169,174 @@
       <c r="Z135" s="1"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="9" t="s">
+      <c r="A136" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B136" s="11" t="s">
+      <c r="B136" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C136" s="11" t="s">
+      <c r="C136" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D136" s="11"/>
-      <c r="E136" s="11"/>
-      <c r="F136" s="11"/>
-      <c r="G136" s="11"/>
-      <c r="H136" s="11"/>
-      <c r="I136" s="11"/>
-      <c r="J136" s="11"/>
-      <c r="K136" s="11"/>
-      <c r="L136" s="11"/>
-      <c r="M136" s="11"/>
-      <c r="N136" s="11"/>
-      <c r="O136" s="11"/>
-      <c r="P136" s="11"/>
-      <c r="Q136" s="11"/>
-      <c r="R136" s="11"/>
-      <c r="S136" s="11"/>
-      <c r="T136" s="11"/>
-      <c r="U136" s="11"/>
-      <c r="V136" s="11"/>
-      <c r="W136" s="11"/>
-      <c r="X136" s="11"/>
-      <c r="Y136" s="11"/>
-      <c r="Z136" s="12"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
+      <c r="K136" s="1"/>
+      <c r="L136" s="1"/>
+      <c r="M136" s="1"/>
+      <c r="N136" s="1"/>
+      <c r="O136" s="1"/>
+      <c r="P136" s="1"/>
+      <c r="Q136" s="1"/>
+      <c r="R136" s="1"/>
+      <c r="S136" s="1"/>
+      <c r="T136" s="1"/>
+      <c r="U136" s="1"/>
+      <c r="V136" s="1"/>
+      <c r="W136" s="1"/>
+      <c r="X136" s="1"/>
+      <c r="Y136" s="1"/>
+      <c r="Z136" s="1"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="15" t="s">
+      <c r="A137" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B137" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="C137" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="D137" s="1"/>
-      <c r="E137" s="1"/>
-      <c r="F137" s="1"/>
-      <c r="G137" s="1"/>
-      <c r="H137" s="1"/>
-      <c r="I137" s="1"/>
-      <c r="J137" s="1"/>
-      <c r="K137" s="1"/>
-      <c r="L137" s="1"/>
-      <c r="M137" s="1"/>
-      <c r="N137" s="1"/>
-      <c r="O137" s="1"/>
-      <c r="P137" s="1"/>
-      <c r="Q137" s="1"/>
-      <c r="R137" s="1"/>
-      <c r="S137" s="1"/>
-      <c r="T137" s="1"/>
-      <c r="U137" s="1"/>
-      <c r="V137" s="1"/>
-      <c r="W137" s="1"/>
-      <c r="X137" s="1"/>
-      <c r="Y137" s="1"/>
-      <c r="Z137" s="14"/>
+      <c r="D137" s="11"/>
+      <c r="E137" s="11"/>
+      <c r="F137" s="11"/>
+      <c r="G137" s="11"/>
+      <c r="H137" s="11"/>
+      <c r="I137" s="11"/>
+      <c r="J137" s="11"/>
+      <c r="K137" s="11"/>
+      <c r="L137" s="11"/>
+      <c r="M137" s="11"/>
+      <c r="N137" s="11"/>
+      <c r="O137" s="11"/>
+      <c r="P137" s="11"/>
+      <c r="Q137" s="11"/>
+      <c r="R137" s="11"/>
+      <c r="S137" s="11"/>
+      <c r="T137" s="11"/>
+      <c r="U137" s="11"/>
+      <c r="V137" s="11"/>
+      <c r="W137" s="11"/>
+      <c r="X137" s="11"/>
+      <c r="Y137" s="11"/>
+      <c r="Z137" s="12"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="18" t="s">
+      <c r="A138" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="B138" s="19" t="s">
+      <c r="B138" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C138" s="19" t="s">
+      <c r="C138" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D138" s="19"/>
-      <c r="E138" s="19"/>
-      <c r="F138" s="19"/>
-      <c r="G138" s="19"/>
-      <c r="H138" s="19"/>
-      <c r="I138" s="19"/>
-      <c r="J138" s="19"/>
-      <c r="K138" s="19"/>
-      <c r="L138" s="19"/>
-      <c r="M138" s="19"/>
-      <c r="N138" s="19"/>
-      <c r="O138" s="19"/>
-      <c r="P138" s="19"/>
-      <c r="Q138" s="19"/>
-      <c r="R138" s="19"/>
-      <c r="S138" s="19"/>
-      <c r="T138" s="19"/>
-      <c r="U138" s="19"/>
-      <c r="V138" s="19"/>
-      <c r="W138" s="19"/>
-      <c r="X138" s="19"/>
-      <c r="Y138" s="19"/>
-      <c r="Z138" s="20"/>
+      <c r="D138" s="1"/>
+      <c r="E138" s="1"/>
+      <c r="F138" s="1"/>
+      <c r="G138" s="1"/>
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+      <c r="J138" s="1"/>
+      <c r="K138" s="1"/>
+      <c r="L138" s="1"/>
+      <c r="M138" s="1"/>
+      <c r="N138" s="1"/>
+      <c r="O138" s="1"/>
+      <c r="P138" s="1"/>
+      <c r="Q138" s="1"/>
+      <c r="R138" s="1"/>
+      <c r="S138" s="1"/>
+      <c r="T138" s="1"/>
+      <c r="U138" s="1"/>
+      <c r="V138" s="1"/>
+      <c r="W138" s="1"/>
+      <c r="X138" s="1"/>
+      <c r="Y138" s="1"/>
+      <c r="Z138" s="14"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="9" t="s">
+      <c r="A139" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="B139" s="11" t="s">
+      <c r="B139" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="C139" s="11" t="s">
+      <c r="C139" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="D139" s="11"/>
-      <c r="E139" s="11"/>
-      <c r="F139" s="11"/>
-      <c r="G139" s="11"/>
-      <c r="H139" s="11"/>
-      <c r="I139" s="11"/>
-      <c r="J139" s="11"/>
-      <c r="K139" s="11"/>
-      <c r="L139" s="11"/>
-      <c r="M139" s="11"/>
-      <c r="N139" s="11"/>
-      <c r="O139" s="11"/>
-      <c r="P139" s="11"/>
-      <c r="Q139" s="11"/>
-      <c r="R139" s="11"/>
-      <c r="S139" s="11"/>
-      <c r="T139" s="11"/>
-      <c r="U139" s="11"/>
-      <c r="V139" s="11"/>
-      <c r="W139" s="11"/>
-      <c r="X139" s="11"/>
-      <c r="Y139" s="11"/>
-      <c r="Z139" s="12"/>
+      <c r="D139" s="19"/>
+      <c r="E139" s="19"/>
+      <c r="F139" s="19"/>
+      <c r="G139" s="19"/>
+      <c r="H139" s="19"/>
+      <c r="I139" s="19"/>
+      <c r="J139" s="19"/>
+      <c r="K139" s="19"/>
+      <c r="L139" s="19"/>
+      <c r="M139" s="19"/>
+      <c r="N139" s="19"/>
+      <c r="O139" s="19"/>
+      <c r="P139" s="19"/>
+      <c r="Q139" s="19"/>
+      <c r="R139" s="19"/>
+      <c r="S139" s="19"/>
+      <c r="T139" s="19"/>
+      <c r="U139" s="19"/>
+      <c r="V139" s="19"/>
+      <c r="W139" s="19"/>
+      <c r="X139" s="19"/>
+      <c r="Y139" s="19"/>
+      <c r="Z139" s="20"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="15" t="s">
+      <c r="A140" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B140" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="C140" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="D140" s="1"/>
-      <c r="E140" s="1"/>
-      <c r="F140" s="1"/>
-      <c r="G140" s="1"/>
-      <c r="H140" s="1"/>
-      <c r="I140" s="1"/>
-      <c r="J140" s="1"/>
-      <c r="K140" s="1"/>
-      <c r="L140" s="1"/>
-      <c r="M140" s="1"/>
-      <c r="N140" s="1"/>
-      <c r="O140" s="1"/>
-      <c r="P140" s="1"/>
-      <c r="Q140" s="1"/>
-      <c r="R140" s="1"/>
-      <c r="S140" s="1"/>
-      <c r="T140" s="1"/>
-      <c r="U140" s="1"/>
-      <c r="V140" s="1"/>
-      <c r="W140" s="1"/>
-      <c r="X140" s="1"/>
-      <c r="Y140" s="1"/>
-      <c r="Z140" s="14"/>
+      <c r="D140" s="11"/>
+      <c r="E140" s="11"/>
+      <c r="F140" s="11"/>
+      <c r="G140" s="11"/>
+      <c r="H140" s="11"/>
+      <c r="I140" s="11"/>
+      <c r="J140" s="11"/>
+      <c r="K140" s="11"/>
+      <c r="L140" s="11"/>
+      <c r="M140" s="11"/>
+      <c r="N140" s="11"/>
+      <c r="O140" s="11"/>
+      <c r="P140" s="11"/>
+      <c r="Q140" s="11"/>
+      <c r="R140" s="11"/>
+      <c r="S140" s="11"/>
+      <c r="T140" s="11"/>
+      <c r="U140" s="11"/>
+      <c r="V140" s="11"/>
+      <c r="W140" s="11"/>
+      <c r="X140" s="11"/>
+      <c r="Y140" s="11"/>
+      <c r="Z140" s="12"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="15" t="s">
@@ -6367,109 +6373,109 @@
       <c r="Z141" s="14"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="18" t="s">
+      <c r="A142" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B142" s="19" t="s">
+      <c r="B142" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C142" s="19" t="s">
+      <c r="C142" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D142" s="19"/>
-      <c r="E142" s="19"/>
-      <c r="F142" s="19"/>
-      <c r="G142" s="19"/>
-      <c r="H142" s="19"/>
-      <c r="I142" s="19"/>
-      <c r="J142" s="19"/>
-      <c r="K142" s="19"/>
-      <c r="L142" s="19"/>
-      <c r="M142" s="19"/>
-      <c r="N142" s="19"/>
-      <c r="O142" s="19"/>
-      <c r="P142" s="19"/>
-      <c r="Q142" s="19"/>
-      <c r="R142" s="19"/>
-      <c r="S142" s="19"/>
-      <c r="T142" s="19"/>
-      <c r="U142" s="19"/>
-      <c r="V142" s="19"/>
-      <c r="W142" s="19"/>
-      <c r="X142" s="19"/>
-      <c r="Y142" s="19"/>
-      <c r="Z142" s="20"/>
+      <c r="D142" s="1"/>
+      <c r="E142" s="1"/>
+      <c r="F142" s="1"/>
+      <c r="G142" s="1"/>
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+      <c r="J142" s="1"/>
+      <c r="K142" s="1"/>
+      <c r="L142" s="1"/>
+      <c r="M142" s="1"/>
+      <c r="N142" s="1"/>
+      <c r="O142" s="1"/>
+      <c r="P142" s="1"/>
+      <c r="Q142" s="1"/>
+      <c r="R142" s="1"/>
+      <c r="S142" s="1"/>
+      <c r="T142" s="1"/>
+      <c r="U142" s="1"/>
+      <c r="V142" s="1"/>
+      <c r="W142" s="1"/>
+      <c r="X142" s="1"/>
+      <c r="Y142" s="1"/>
+      <c r="Z142" s="14"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="9" t="s">
+      <c r="A143" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="B143" s="11" t="s">
+      <c r="B143" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="C143" s="11" t="s">
+      <c r="C143" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="D143" s="11"/>
-      <c r="E143" s="11"/>
-      <c r="F143" s="11"/>
-      <c r="G143" s="11"/>
-      <c r="H143" s="11"/>
-      <c r="I143" s="11"/>
-      <c r="J143" s="11"/>
-      <c r="K143" s="11"/>
-      <c r="L143" s="11"/>
-      <c r="M143" s="11"/>
-      <c r="N143" s="11"/>
-      <c r="O143" s="11"/>
-      <c r="P143" s="11"/>
-      <c r="Q143" s="11"/>
-      <c r="R143" s="11"/>
-      <c r="S143" s="11"/>
-      <c r="T143" s="11"/>
-      <c r="U143" s="11"/>
-      <c r="V143" s="11"/>
-      <c r="W143" s="11"/>
-      <c r="X143" s="11"/>
-      <c r="Y143" s="11"/>
-      <c r="Z143" s="12"/>
+      <c r="D143" s="19"/>
+      <c r="E143" s="19"/>
+      <c r="F143" s="19"/>
+      <c r="G143" s="19"/>
+      <c r="H143" s="19"/>
+      <c r="I143" s="19"/>
+      <c r="J143" s="19"/>
+      <c r="K143" s="19"/>
+      <c r="L143" s="19"/>
+      <c r="M143" s="19"/>
+      <c r="N143" s="19"/>
+      <c r="O143" s="19"/>
+      <c r="P143" s="19"/>
+      <c r="Q143" s="19"/>
+      <c r="R143" s="19"/>
+      <c r="S143" s="19"/>
+      <c r="T143" s="19"/>
+      <c r="U143" s="19"/>
+      <c r="V143" s="19"/>
+      <c r="W143" s="19"/>
+      <c r="X143" s="19"/>
+      <c r="Y143" s="19"/>
+      <c r="Z143" s="20"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="34" t="s">
+      <c r="A144" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B144" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="C144" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="D144" s="1"/>
-      <c r="E144" s="1"/>
-      <c r="F144" s="1"/>
-      <c r="G144" s="1"/>
-      <c r="H144" s="1"/>
-      <c r="I144" s="1"/>
-      <c r="J144" s="1"/>
-      <c r="K144" s="1"/>
-      <c r="L144" s="1"/>
-      <c r="M144" s="1"/>
-      <c r="N144" s="1"/>
-      <c r="O144" s="1"/>
-      <c r="P144" s="1"/>
-      <c r="Q144" s="1"/>
-      <c r="R144" s="1"/>
-      <c r="S144" s="1"/>
-      <c r="T144" s="1"/>
-      <c r="U144" s="1"/>
-      <c r="V144" s="1"/>
-      <c r="W144" s="1"/>
-      <c r="X144" s="1"/>
-      <c r="Y144" s="1"/>
-      <c r="Z144" s="14"/>
+      <c r="D144" s="11"/>
+      <c r="E144" s="11"/>
+      <c r="F144" s="11"/>
+      <c r="G144" s="11"/>
+      <c r="H144" s="11"/>
+      <c r="I144" s="11"/>
+      <c r="J144" s="11"/>
+      <c r="K144" s="11"/>
+      <c r="L144" s="11"/>
+      <c r="M144" s="11"/>
+      <c r="N144" s="11"/>
+      <c r="O144" s="11"/>
+      <c r="P144" s="11"/>
+      <c r="Q144" s="11"/>
+      <c r="R144" s="11"/>
+      <c r="S144" s="11"/>
+      <c r="T144" s="11"/>
+      <c r="U144" s="11"/>
+      <c r="V144" s="11"/>
+      <c r="W144" s="11"/>
+      <c r="X144" s="11"/>
+      <c r="Y144" s="11"/>
+      <c r="Z144" s="12"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="15" t="s">
+      <c r="A145" s="34" t="s">
         <v>249</v>
       </c>
       <c r="B145" s="1" t="s">
@@ -6503,77 +6509,83 @@
       <c r="Z145" s="14"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="18" t="s">
+      <c r="A146" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="B146" s="19" t="s">
+      <c r="B146" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C146" s="19" t="s">
+      <c r="C146" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D146" s="1"/>
+      <c r="E146" s="1"/>
+      <c r="F146" s="1"/>
+      <c r="G146" s="1"/>
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+      <c r="J146" s="1"/>
+      <c r="K146" s="1"/>
+      <c r="L146" s="1"/>
+      <c r="M146" s="1"/>
+      <c r="N146" s="1"/>
+      <c r="O146" s="1"/>
+      <c r="P146" s="1"/>
+      <c r="Q146" s="1"/>
+      <c r="R146" s="1"/>
+      <c r="S146" s="1"/>
+      <c r="T146" s="1"/>
+      <c r="U146" s="1"/>
+      <c r="V146" s="1"/>
+      <c r="W146" s="1"/>
+      <c r="X146" s="1"/>
+      <c r="Y146" s="1"/>
+      <c r="Z146" s="14"/>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B147" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="C147" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D146" s="19"/>
-      <c r="E146" s="19"/>
-      <c r="F146" s="19"/>
-      <c r="G146" s="19"/>
-      <c r="H146" s="19"/>
-      <c r="I146" s="19"/>
-      <c r="J146" s="19"/>
-      <c r="K146" s="19"/>
-      <c r="L146" s="19"/>
-      <c r="M146" s="19"/>
-      <c r="N146" s="19"/>
-      <c r="O146" s="19"/>
-      <c r="P146" s="19"/>
-      <c r="Q146" s="19"/>
-      <c r="R146" s="19"/>
-      <c r="S146" s="19"/>
-      <c r="T146" s="19"/>
-      <c r="U146" s="19"/>
-      <c r="V146" s="19"/>
-      <c r="W146" s="19"/>
-      <c r="X146" s="19"/>
-      <c r="Y146" s="19"/>
-      <c r="Z146" s="20"/>
-    </row>
-    <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D147" s="1"/>
-      <c r="E147" s="1"/>
-      <c r="F147" s="1"/>
-      <c r="G147" s="1"/>
-      <c r="H147" s="1"/>
-      <c r="I147" s="1"/>
-      <c r="J147" s="1"/>
-      <c r="K147" s="1"/>
-      <c r="L147" s="1"/>
-      <c r="M147" s="1"/>
-      <c r="N147" s="1"/>
-      <c r="O147" s="1"/>
-      <c r="P147" s="1"/>
-      <c r="Q147" s="1"/>
-      <c r="R147" s="1"/>
-      <c r="S147" s="1"/>
-      <c r="T147" s="1"/>
-      <c r="U147" s="1"/>
-      <c r="V147" s="1"/>
-      <c r="W147" s="1"/>
-      <c r="X147" s="1"/>
-      <c r="Y147" s="1"/>
-      <c r="Z147" s="1"/>
+      <c r="D147" s="19"/>
+      <c r="E147" s="19"/>
+      <c r="F147" s="19"/>
+      <c r="G147" s="19"/>
+      <c r="H147" s="19"/>
+      <c r="I147" s="19"/>
+      <c r="J147" s="19"/>
+      <c r="K147" s="19"/>
+      <c r="L147" s="19"/>
+      <c r="M147" s="19"/>
+      <c r="N147" s="19"/>
+      <c r="O147" s="19"/>
+      <c r="P147" s="19"/>
+      <c r="Q147" s="19"/>
+      <c r="R147" s="19"/>
+      <c r="S147" s="19"/>
+      <c r="T147" s="19"/>
+      <c r="U147" s="19"/>
+      <c r="V147" s="19"/>
+      <c r="W147" s="19"/>
+      <c r="X147" s="19"/>
+      <c r="Y147" s="19"/>
+      <c r="Z147" s="20"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="1"/>
-      <c r="B148" s="1"/>
-      <c r="C148" s="1"/>
+      <c r="A148" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>255</v>
+      </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
@@ -6599,73 +6611,73 @@
       <c r="Z148" s="1"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2"/>
-      <c r="F149" s="2"/>
-      <c r="G149" s="2"/>
-      <c r="H149" s="2"/>
-      <c r="I149" s="2"/>
-      <c r="J149" s="2"/>
-      <c r="K149" s="2"/>
-      <c r="L149" s="2"/>
-      <c r="M149" s="2"/>
-      <c r="N149" s="2"/>
-      <c r="O149" s="2"/>
-      <c r="P149" s="2"/>
-      <c r="Q149" s="2"/>
-      <c r="R149" s="2"/>
-      <c r="S149" s="2"/>
-      <c r="T149" s="2"/>
-      <c r="U149" s="2"/>
-      <c r="V149" s="2"/>
-      <c r="W149" s="2"/>
-      <c r="X149" s="2"/>
-      <c r="Y149" s="2"/>
-      <c r="Z149" s="2"/>
+      <c r="A149" s="1"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1"/>
+      <c r="F149" s="1"/>
+      <c r="G149" s="1"/>
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+      <c r="J149" s="1"/>
+      <c r="K149" s="1"/>
+      <c r="L149" s="1"/>
+      <c r="M149" s="1"/>
+      <c r="N149" s="1"/>
+      <c r="O149" s="1"/>
+      <c r="P149" s="1"/>
+      <c r="Q149" s="1"/>
+      <c r="R149" s="1"/>
+      <c r="S149" s="1"/>
+      <c r="T149" s="1"/>
+      <c r="U149" s="1"/>
+      <c r="V149" s="1"/>
+      <c r="W149" s="1"/>
+      <c r="X149" s="1"/>
+      <c r="Y149" s="1"/>
+      <c r="Z149" s="1"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C150" s="1" t="s">
+      <c r="A150" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D150" s="1"/>
-      <c r="E150" s="1"/>
-      <c r="F150" s="1"/>
-      <c r="G150" s="1"/>
-      <c r="H150" s="1"/>
-      <c r="I150" s="1"/>
-      <c r="J150" s="1"/>
-      <c r="K150" s="1"/>
-      <c r="L150" s="1"/>
-      <c r="M150" s="1"/>
-      <c r="N150" s="1"/>
-      <c r="O150" s="1"/>
-      <c r="P150" s="1"/>
-      <c r="Q150" s="1"/>
-      <c r="R150" s="1"/>
-      <c r="S150" s="1"/>
-      <c r="T150" s="1"/>
-      <c r="U150" s="1"/>
-      <c r="V150" s="1"/>
-      <c r="W150" s="1"/>
-      <c r="X150" s="1"/>
-      <c r="Y150" s="1"/>
-      <c r="Z150" s="1"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+      <c r="H150" s="2"/>
+      <c r="I150" s="2"/>
+      <c r="J150" s="2"/>
+      <c r="K150" s="2"/>
+      <c r="L150" s="2"/>
+      <c r="M150" s="2"/>
+      <c r="N150" s="2"/>
+      <c r="O150" s="2"/>
+      <c r="P150" s="2"/>
+      <c r="Q150" s="2"/>
+      <c r="R150" s="2"/>
+      <c r="S150" s="2"/>
+      <c r="T150" s="2"/>
+      <c r="U150" s="2"/>
+      <c r="V150" s="2"/>
+      <c r="W150" s="2"/>
+      <c r="X150" s="2"/>
+      <c r="Y150" s="2"/>
+      <c r="Z150" s="2"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="1"/>
-      <c r="B151" s="1"/>
-      <c r="C151" s="1"/>
+      <c r="A151" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
@@ -6691,68 +6703,62 @@
       <c r="Z151" s="1"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B152" s="2"/>
-      <c r="C152" s="2"/>
-      <c r="D152" s="2"/>
-      <c r="E152" s="2"/>
-      <c r="F152" s="2"/>
-      <c r="G152" s="2"/>
-      <c r="H152" s="2"/>
-      <c r="I152" s="2"/>
-      <c r="J152" s="2"/>
-      <c r="K152" s="2"/>
-      <c r="L152" s="2"/>
-      <c r="M152" s="2"/>
-      <c r="N152" s="2"/>
-      <c r="O152" s="2"/>
-      <c r="P152" s="2"/>
-      <c r="Q152" s="2"/>
-      <c r="R152" s="2"/>
-      <c r="S152" s="2"/>
-      <c r="T152" s="2"/>
-      <c r="U152" s="2"/>
-      <c r="V152" s="2"/>
-      <c r="W152" s="2"/>
-      <c r="X152" s="2"/>
-      <c r="Y152" s="2"/>
-      <c r="Z152" s="2"/>
+      <c r="A152" s="1"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
+      <c r="E152" s="1"/>
+      <c r="F152" s="1"/>
+      <c r="G152" s="1"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="1"/>
+      <c r="J152" s="1"/>
+      <c r="K152" s="1"/>
+      <c r="L152" s="1"/>
+      <c r="M152" s="1"/>
+      <c r="N152" s="1"/>
+      <c r="O152" s="1"/>
+      <c r="P152" s="1"/>
+      <c r="Q152" s="1"/>
+      <c r="R152" s="1"/>
+      <c r="S152" s="1"/>
+      <c r="T152" s="1"/>
+      <c r="U152" s="1"/>
+      <c r="V152" s="1"/>
+      <c r="W152" s="1"/>
+      <c r="X152" s="1"/>
+      <c r="Y152" s="1"/>
+      <c r="Z152" s="1"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D153" s="1"/>
-      <c r="E153" s="1"/>
-      <c r="F153" s="1"/>
-      <c r="G153" s="1"/>
-      <c r="H153" s="1"/>
-      <c r="I153" s="1"/>
-      <c r="J153" s="1"/>
-      <c r="K153" s="1"/>
-      <c r="L153" s="1"/>
-      <c r="M153" s="1"/>
-      <c r="N153" s="1"/>
-      <c r="O153" s="1"/>
-      <c r="P153" s="1"/>
-      <c r="Q153" s="1"/>
-      <c r="R153" s="1"/>
-      <c r="S153" s="1"/>
-      <c r="T153" s="1"/>
-      <c r="U153" s="1"/>
-      <c r="V153" s="1"/>
-      <c r="W153" s="1"/>
-      <c r="X153" s="1"/>
-      <c r="Y153" s="1"/>
-      <c r="Z153" s="1"/>
+      <c r="A153" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2"/>
+      <c r="H153" s="2"/>
+      <c r="I153" s="2"/>
+      <c r="J153" s="2"/>
+      <c r="K153" s="2"/>
+      <c r="L153" s="2"/>
+      <c r="M153" s="2"/>
+      <c r="N153" s="2"/>
+      <c r="O153" s="2"/>
+      <c r="P153" s="2"/>
+      <c r="Q153" s="2"/>
+      <c r="R153" s="2"/>
+      <c r="S153" s="2"/>
+      <c r="T153" s="2"/>
+      <c r="U153" s="2"/>
+      <c r="V153" s="2"/>
+      <c r="W153" s="2"/>
+      <c r="X153" s="2"/>
+      <c r="Y153" s="2"/>
+      <c r="Z153" s="2"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="1" t="s">
@@ -6993,9 +6999,15 @@
       <c r="Z160" s="1"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="1"/>
-      <c r="B161" s="1"/>
-      <c r="C161" s="1"/>
+      <c r="A161" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>274</v>
+      </c>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
@@ -7021,68 +7033,62 @@
       <c r="Z161" s="1"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B162" s="2"/>
-      <c r="C162" s="2"/>
-      <c r="D162" s="2"/>
-      <c r="E162" s="2"/>
-      <c r="F162" s="2"/>
-      <c r="G162" s="2"/>
-      <c r="H162" s="2"/>
-      <c r="I162" s="2"/>
-      <c r="J162" s="2"/>
-      <c r="K162" s="2"/>
-      <c r="L162" s="2"/>
-      <c r="M162" s="2"/>
-      <c r="N162" s="2"/>
-      <c r="O162" s="2"/>
-      <c r="P162" s="2"/>
-      <c r="Q162" s="2"/>
-      <c r="R162" s="2"/>
-      <c r="S162" s="2"/>
-      <c r="T162" s="2"/>
-      <c r="U162" s="2"/>
-      <c r="V162" s="2"/>
-      <c r="W162" s="2"/>
-      <c r="X162" s="2"/>
-      <c r="Y162" s="2"/>
-      <c r="Z162" s="2"/>
+      <c r="A162" s="1"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
+      <c r="E162" s="1"/>
+      <c r="F162" s="1"/>
+      <c r="G162" s="1"/>
+      <c r="H162" s="1"/>
+      <c r="I162" s="1"/>
+      <c r="J162" s="1"/>
+      <c r="K162" s="1"/>
+      <c r="L162" s="1"/>
+      <c r="M162" s="1"/>
+      <c r="N162" s="1"/>
+      <c r="O162" s="1"/>
+      <c r="P162" s="1"/>
+      <c r="Q162" s="1"/>
+      <c r="R162" s="1"/>
+      <c r="S162" s="1"/>
+      <c r="T162" s="1"/>
+      <c r="U162" s="1"/>
+      <c r="V162" s="1"/>
+      <c r="W162" s="1"/>
+      <c r="X162" s="1"/>
+      <c r="Y162" s="1"/>
+      <c r="Z162" s="1"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C163" s="1" t="s">
+      <c r="A163" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D163" s="1"/>
-      <c r="E163" s="1"/>
-      <c r="F163" s="1"/>
-      <c r="G163" s="1"/>
-      <c r="H163" s="1"/>
-      <c r="I163" s="1"/>
-      <c r="J163" s="1"/>
-      <c r="K163" s="1"/>
-      <c r="L163" s="1"/>
-      <c r="M163" s="1"/>
-      <c r="N163" s="1"/>
-      <c r="O163" s="1"/>
-      <c r="P163" s="1"/>
-      <c r="Q163" s="1"/>
-      <c r="R163" s="1"/>
-      <c r="S163" s="1"/>
-      <c r="T163" s="1"/>
-      <c r="U163" s="1"/>
-      <c r="V163" s="1"/>
-      <c r="W163" s="1"/>
-      <c r="X163" s="1"/>
-      <c r="Y163" s="1"/>
-      <c r="Z163" s="1"/>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2"/>
+      <c r="G163" s="2"/>
+      <c r="H163" s="2"/>
+      <c r="I163" s="2"/>
+      <c r="J163" s="2"/>
+      <c r="K163" s="2"/>
+      <c r="L163" s="2"/>
+      <c r="M163" s="2"/>
+      <c r="N163" s="2"/>
+      <c r="O163" s="2"/>
+      <c r="P163" s="2"/>
+      <c r="Q163" s="2"/>
+      <c r="R163" s="2"/>
+      <c r="S163" s="2"/>
+      <c r="T163" s="2"/>
+      <c r="U163" s="2"/>
+      <c r="V163" s="2"/>
+      <c r="W163" s="2"/>
+      <c r="X163" s="2"/>
+      <c r="Y163" s="2"/>
+      <c r="Z163" s="2"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="1" t="s">
@@ -7119,72 +7125,72 @@
       <c r="Z164" s="1"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="22" t="s">
+      <c r="A165" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B165" s="22" t="s">
+      <c r="B165" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C165" s="22" t="s">
+      <c r="C165" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D165" s="21"/>
-      <c r="E165" s="21"/>
-      <c r="F165" s="21"/>
-      <c r="G165" s="21"/>
-      <c r="H165" s="21"/>
-      <c r="I165" s="21"/>
-      <c r="J165" s="21"/>
-      <c r="K165" s="21"/>
-      <c r="L165" s="21"/>
-      <c r="M165" s="21"/>
-      <c r="N165" s="21"/>
-      <c r="O165" s="21"/>
-      <c r="P165" s="21"/>
-      <c r="Q165" s="21"/>
-      <c r="R165" s="21"/>
-      <c r="S165" s="21"/>
-      <c r="T165" s="21"/>
-      <c r="U165" s="21"/>
-      <c r="V165" s="21"/>
-      <c r="W165" s="21"/>
-      <c r="X165" s="21"/>
-      <c r="Y165" s="21"/>
-      <c r="Z165" s="21"/>
+      <c r="D165" s="1"/>
+      <c r="E165" s="1"/>
+      <c r="F165" s="1"/>
+      <c r="G165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+      <c r="J165" s="1"/>
+      <c r="K165" s="1"/>
+      <c r="L165" s="1"/>
+      <c r="M165" s="1"/>
+      <c r="N165" s="1"/>
+      <c r="O165" s="1"/>
+      <c r="P165" s="1"/>
+      <c r="Q165" s="1"/>
+      <c r="R165" s="1"/>
+      <c r="S165" s="1"/>
+      <c r="T165" s="1"/>
+      <c r="U165" s="1"/>
+      <c r="V165" s="1"/>
+      <c r="W165" s="1"/>
+      <c r="X165" s="1"/>
+      <c r="Y165" s="1"/>
+      <c r="Z165" s="1"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="7" t="s">
+      <c r="A166" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="B166" s="7" t="s">
+      <c r="B166" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="C166" s="7" t="s">
+      <c r="C166" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="D166" s="1"/>
-      <c r="E166" s="1"/>
-      <c r="F166" s="1"/>
-      <c r="G166" s="1"/>
-      <c r="H166" s="1"/>
-      <c r="I166" s="1"/>
-      <c r="J166" s="1"/>
-      <c r="K166" s="1"/>
-      <c r="L166" s="1"/>
-      <c r="M166" s="1"/>
-      <c r="N166" s="1"/>
-      <c r="O166" s="1"/>
-      <c r="P166" s="1"/>
-      <c r="Q166" s="1"/>
-      <c r="R166" s="1"/>
-      <c r="S166" s="1"/>
-      <c r="T166" s="1"/>
-      <c r="U166" s="1"/>
-      <c r="V166" s="1"/>
-      <c r="W166" s="1"/>
-      <c r="X166" s="1"/>
-      <c r="Y166" s="1"/>
-      <c r="Z166" s="1"/>
+      <c r="D166" s="21"/>
+      <c r="E166" s="21"/>
+      <c r="F166" s="21"/>
+      <c r="G166" s="21"/>
+      <c r="H166" s="21"/>
+      <c r="I166" s="21"/>
+      <c r="J166" s="21"/>
+      <c r="K166" s="21"/>
+      <c r="L166" s="21"/>
+      <c r="M166" s="21"/>
+      <c r="N166" s="21"/>
+      <c r="O166" s="21"/>
+      <c r="P166" s="21"/>
+      <c r="Q166" s="21"/>
+      <c r="R166" s="21"/>
+      <c r="S166" s="21"/>
+      <c r="T166" s="21"/>
+      <c r="U166" s="21"/>
+      <c r="V166" s="21"/>
+      <c r="W166" s="21"/>
+      <c r="X166" s="21"/>
+      <c r="Y166" s="21"/>
+      <c r="Z166" s="21"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="7" t="s">
@@ -7224,7 +7230,7 @@
       <c r="A168" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="B168" s="17" t="s">
+      <c r="B168" s="7" t="s">
         <v>284</v>
       </c>
       <c r="C168" s="7" t="s">
@@ -7258,7 +7264,7 @@
       <c r="A169" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="B169" s="7" t="s">
+      <c r="B169" s="17" t="s">
         <v>286</v>
       </c>
       <c r="C169" s="7" t="s">
@@ -7326,7 +7332,7 @@
       <c r="A171" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B171" s="8" t="s">
+      <c r="B171" s="7" t="s">
         <v>290</v>
       </c>
       <c r="C171" s="7" t="s">
@@ -7357,9 +7363,15 @@
       <c r="Z171" s="1"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="7"/>
-      <c r="B172" s="7"/>
-      <c r="C172" s="1"/>
+      <c r="A172" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>293</v>
+      </c>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
@@ -7385,73 +7397,73 @@
       <c r="Z172" s="1"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="2" t="s">
+      <c r="A173" s="7"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
+      <c r="E173" s="1"/>
+      <c r="F173" s="1"/>
+      <c r="G173" s="1"/>
+      <c r="H173" s="1"/>
+      <c r="I173" s="1"/>
+      <c r="J173" s="1"/>
+      <c r="K173" s="1"/>
+      <c r="L173" s="1"/>
+      <c r="M173" s="1"/>
+      <c r="N173" s="1"/>
+      <c r="O173" s="1"/>
+      <c r="P173" s="1"/>
+      <c r="Q173" s="1"/>
+      <c r="R173" s="1"/>
+      <c r="S173" s="1"/>
+      <c r="T173" s="1"/>
+      <c r="U173" s="1"/>
+      <c r="V173" s="1"/>
+      <c r="W173" s="1"/>
+      <c r="X173" s="1"/>
+      <c r="Y173" s="1"/>
+      <c r="Z173" s="1"/>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B173" s="2"/>
-      <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
-      <c r="E173" s="2"/>
-      <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-      <c r="H173" s="2"/>
-      <c r="I173" s="2"/>
-      <c r="J173" s="2"/>
-      <c r="K173" s="2"/>
-      <c r="L173" s="2"/>
-      <c r="M173" s="2"/>
-      <c r="N173" s="2"/>
-      <c r="O173" s="2"/>
-      <c r="P173" s="2"/>
-      <c r="Q173" s="2"/>
-      <c r="R173" s="2"/>
-      <c r="S173" s="2"/>
-      <c r="T173" s="2"/>
-      <c r="U173" s="2"/>
-      <c r="V173" s="2"/>
-      <c r="W173" s="2"/>
-      <c r="X173" s="2"/>
-      <c r="Y173" s="2"/>
-      <c r="Z173" s="2"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D174" s="1"/>
-      <c r="E174" s="1"/>
-      <c r="F174" s="1"/>
-      <c r="G174" s="1"/>
-      <c r="H174" s="1"/>
-      <c r="I174" s="1"/>
-      <c r="J174" s="1"/>
-      <c r="K174" s="1"/>
-      <c r="L174" s="1"/>
-      <c r="M174" s="1"/>
-      <c r="N174" s="1"/>
-      <c r="O174" s="1"/>
-      <c r="P174" s="1"/>
-      <c r="Q174" s="1"/>
-      <c r="R174" s="1"/>
-      <c r="S174" s="1"/>
-      <c r="T174" s="1"/>
-      <c r="U174" s="1"/>
-      <c r="V174" s="1"/>
-      <c r="W174" s="1"/>
-      <c r="X174" s="1"/>
-      <c r="Y174" s="1"/>
-      <c r="Z174" s="1"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+      <c r="I174" s="2"/>
+      <c r="J174" s="2"/>
+      <c r="K174" s="2"/>
+      <c r="L174" s="2"/>
+      <c r="M174" s="2"/>
+      <c r="N174" s="2"/>
+      <c r="O174" s="2"/>
+      <c r="P174" s="2"/>
+      <c r="Q174" s="2"/>
+      <c r="R174" s="2"/>
+      <c r="S174" s="2"/>
+      <c r="T174" s="2"/>
+      <c r="U174" s="2"/>
+      <c r="V174" s="2"/>
+      <c r="W174" s="2"/>
+      <c r="X174" s="2"/>
+      <c r="Y174" s="2"/>
+      <c r="Z174" s="2"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="1"/>
-      <c r="B175" s="1"/>
-      <c r="C175" s="1"/>
+      <c r="A175" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>295</v>
+      </c>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
@@ -7477,170 +7489,164 @@
       <c r="Z175" s="1"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="B176" s="2"/>
-      <c r="C176" s="2"/>
-      <c r="D176" s="2"/>
-      <c r="E176" s="2"/>
-      <c r="F176" s="2"/>
-      <c r="G176" s="2"/>
-      <c r="H176" s="2"/>
-      <c r="I176" s="2"/>
-      <c r="J176" s="2"/>
-      <c r="K176" s="2"/>
-      <c r="L176" s="2"/>
-      <c r="M176" s="2"/>
-      <c r="N176" s="2"/>
-      <c r="O176" s="2"/>
-      <c r="P176" s="2"/>
-      <c r="Q176" s="2"/>
-      <c r="R176" s="2"/>
-      <c r="S176" s="2"/>
-      <c r="T176" s="2"/>
-      <c r="U176" s="2"/>
-      <c r="V176" s="2"/>
-      <c r="W176" s="2"/>
-      <c r="X176" s="2"/>
-      <c r="Y176" s="2"/>
-      <c r="Z176" s="2"/>
+      <c r="A176" s="1"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
+      <c r="E176" s="1"/>
+      <c r="F176" s="1"/>
+      <c r="G176" s="1"/>
+      <c r="H176" s="1"/>
+      <c r="I176" s="1"/>
+      <c r="J176" s="1"/>
+      <c r="K176" s="1"/>
+      <c r="L176" s="1"/>
+      <c r="M176" s="1"/>
+      <c r="N176" s="1"/>
+      <c r="O176" s="1"/>
+      <c r="P176" s="1"/>
+      <c r="Q176" s="1"/>
+      <c r="R176" s="1"/>
+      <c r="S176" s="1"/>
+      <c r="T176" s="1"/>
+      <c r="U176" s="1"/>
+      <c r="V176" s="1"/>
+      <c r="W176" s="1"/>
+      <c r="X176" s="1"/>
+      <c r="Y176" s="1"/>
+      <c r="Z176" s="1"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="B177" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="C177" s="11" t="s">
+      <c r="A177" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D177" s="11"/>
-      <c r="E177" s="11"/>
-      <c r="F177" s="11"/>
-      <c r="G177" s="11"/>
-      <c r="H177" s="11"/>
-      <c r="I177" s="11"/>
-      <c r="J177" s="11"/>
-      <c r="K177" s="11"/>
-      <c r="L177" s="11"/>
-      <c r="M177" s="11"/>
-      <c r="N177" s="11"/>
-      <c r="O177" s="11"/>
-      <c r="P177" s="11"/>
-      <c r="Q177" s="11"/>
-      <c r="R177" s="11"/>
-      <c r="S177" s="11"/>
-      <c r="T177" s="11"/>
-      <c r="U177" s="11"/>
-      <c r="V177" s="11"/>
-      <c r="W177" s="11"/>
-      <c r="X177" s="11"/>
-      <c r="Y177" s="11"/>
-      <c r="Z177" s="12"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="2"/>
+      <c r="I177" s="2"/>
+      <c r="J177" s="2"/>
+      <c r="K177" s="2"/>
+      <c r="L177" s="2"/>
+      <c r="M177" s="2"/>
+      <c r="N177" s="2"/>
+      <c r="O177" s="2"/>
+      <c r="P177" s="2"/>
+      <c r="Q177" s="2"/>
+      <c r="R177" s="2"/>
+      <c r="S177" s="2"/>
+      <c r="T177" s="2"/>
+      <c r="U177" s="2"/>
+      <c r="V177" s="2"/>
+      <c r="W177" s="2"/>
+      <c r="X177" s="2"/>
+      <c r="Y177" s="2"/>
+      <c r="Z177" s="2"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="18" t="s">
+      <c r="A178" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="B178" s="19" t="s">
+      <c r="B178" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="C178" s="19" t="s">
+      <c r="C178" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="D178" s="19"/>
-      <c r="E178" s="19"/>
-      <c r="F178" s="19"/>
-      <c r="G178" s="19"/>
-      <c r="H178" s="19"/>
-      <c r="I178" s="19"/>
-      <c r="J178" s="19"/>
-      <c r="K178" s="19"/>
-      <c r="L178" s="19"/>
-      <c r="M178" s="19"/>
-      <c r="N178" s="19"/>
-      <c r="O178" s="19"/>
-      <c r="P178" s="19"/>
-      <c r="Q178" s="19"/>
-      <c r="R178" s="19"/>
-      <c r="S178" s="19"/>
-      <c r="T178" s="19"/>
-      <c r="U178" s="19"/>
-      <c r="V178" s="19"/>
-      <c r="W178" s="19"/>
-      <c r="X178" s="19"/>
-      <c r="Y178" s="19"/>
-      <c r="Z178" s="20"/>
+      <c r="D178" s="11"/>
+      <c r="E178" s="11"/>
+      <c r="F178" s="11"/>
+      <c r="G178" s="11"/>
+      <c r="H178" s="11"/>
+      <c r="I178" s="11"/>
+      <c r="J178" s="11"/>
+      <c r="K178" s="11"/>
+      <c r="L178" s="11"/>
+      <c r="M178" s="11"/>
+      <c r="N178" s="11"/>
+      <c r="O178" s="11"/>
+      <c r="P178" s="11"/>
+      <c r="Q178" s="11"/>
+      <c r="R178" s="11"/>
+      <c r="S178" s="11"/>
+      <c r="T178" s="11"/>
+      <c r="U178" s="11"/>
+      <c r="V178" s="11"/>
+      <c r="W178" s="11"/>
+      <c r="X178" s="11"/>
+      <c r="Y178" s="11"/>
+      <c r="Z178" s="12"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="9" t="s">
+      <c r="A179" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="B179" s="11" t="s">
+      <c r="B179" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="C179" s="11" t="s">
+      <c r="C179" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="D179" s="11"/>
-      <c r="E179" s="11"/>
-      <c r="F179" s="11"/>
-      <c r="G179" s="11"/>
-      <c r="H179" s="11"/>
-      <c r="I179" s="11"/>
-      <c r="J179" s="11"/>
-      <c r="K179" s="11"/>
-      <c r="L179" s="11"/>
-      <c r="M179" s="11"/>
-      <c r="N179" s="11"/>
-      <c r="O179" s="11"/>
-      <c r="P179" s="11"/>
-      <c r="Q179" s="11"/>
-      <c r="R179" s="11"/>
-      <c r="S179" s="11"/>
-      <c r="T179" s="11"/>
-      <c r="U179" s="11"/>
-      <c r="V179" s="11"/>
-      <c r="W179" s="11"/>
-      <c r="X179" s="11"/>
-      <c r="Y179" s="11"/>
-      <c r="Z179" s="12"/>
+      <c r="D179" s="19"/>
+      <c r="E179" s="19"/>
+      <c r="F179" s="19"/>
+      <c r="G179" s="19"/>
+      <c r="H179" s="19"/>
+      <c r="I179" s="19"/>
+      <c r="J179" s="19"/>
+      <c r="K179" s="19"/>
+      <c r="L179" s="19"/>
+      <c r="M179" s="19"/>
+      <c r="N179" s="19"/>
+      <c r="O179" s="19"/>
+      <c r="P179" s="19"/>
+      <c r="Q179" s="19"/>
+      <c r="R179" s="19"/>
+      <c r="S179" s="19"/>
+      <c r="T179" s="19"/>
+      <c r="U179" s="19"/>
+      <c r="V179" s="19"/>
+      <c r="W179" s="19"/>
+      <c r="X179" s="19"/>
+      <c r="Y179" s="19"/>
+      <c r="Z179" s="20"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="34" t="s">
+      <c r="A180" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="B180" s="22" t="s">
+      <c r="B180" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="C180" s="22" t="s">
+      <c r="C180" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="D180" s="22"/>
-      <c r="E180" s="22"/>
-      <c r="F180" s="22"/>
-      <c r="G180" s="22"/>
-      <c r="H180" s="22"/>
-      <c r="I180" s="22"/>
-      <c r="J180" s="22"/>
-      <c r="K180" s="22"/>
-      <c r="L180" s="22"/>
-      <c r="M180" s="22"/>
-      <c r="N180" s="22"/>
-      <c r="O180" s="22"/>
-      <c r="P180" s="22"/>
-      <c r="Q180" s="22"/>
-      <c r="R180" s="22"/>
-      <c r="S180" s="22"/>
-      <c r="T180" s="22"/>
-      <c r="U180" s="22"/>
-      <c r="V180" s="22"/>
-      <c r="W180" s="22"/>
-      <c r="X180" s="22"/>
-      <c r="Y180" s="22"/>
-      <c r="Z180" s="23"/>
+      <c r="D180" s="11"/>
+      <c r="E180" s="11"/>
+      <c r="F180" s="11"/>
+      <c r="G180" s="11"/>
+      <c r="H180" s="11"/>
+      <c r="I180" s="11"/>
+      <c r="J180" s="11"/>
+      <c r="K180" s="11"/>
+      <c r="L180" s="11"/>
+      <c r="M180" s="11"/>
+      <c r="N180" s="11"/>
+      <c r="O180" s="11"/>
+      <c r="P180" s="11"/>
+      <c r="Q180" s="11"/>
+      <c r="R180" s="11"/>
+      <c r="S180" s="11"/>
+      <c r="T180" s="11"/>
+      <c r="U180" s="11"/>
+      <c r="V180" s="11"/>
+      <c r="W180" s="11"/>
+      <c r="X180" s="11"/>
+      <c r="Y180" s="11"/>
+      <c r="Z180" s="12"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="34" t="s">
@@ -7745,116 +7751,116 @@
       <c r="Z183" s="23"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="35" t="s">
+      <c r="A184" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="B184" s="36" t="s">
+      <c r="B184" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C184" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="C184" s="36" t="s">
-        <v>310</v>
-      </c>
-      <c r="D184" s="36"/>
-      <c r="E184" s="36"/>
-      <c r="F184" s="36"/>
-      <c r="G184" s="36"/>
-      <c r="H184" s="36"/>
-      <c r="I184" s="36"/>
-      <c r="J184" s="36"/>
-      <c r="K184" s="36"/>
-      <c r="L184" s="36"/>
-      <c r="M184" s="36"/>
-      <c r="N184" s="36"/>
-      <c r="O184" s="36"/>
-      <c r="P184" s="36"/>
-      <c r="Q184" s="36"/>
-      <c r="R184" s="36"/>
-      <c r="S184" s="36"/>
-      <c r="T184" s="36"/>
-      <c r="U184" s="36"/>
-      <c r="V184" s="36"/>
-      <c r="W184" s="36"/>
-      <c r="X184" s="36"/>
-      <c r="Y184" s="36"/>
-      <c r="Z184" s="37"/>
+      <c r="D184" s="22"/>
+      <c r="E184" s="22"/>
+      <c r="F184" s="22"/>
+      <c r="G184" s="22"/>
+      <c r="H184" s="22"/>
+      <c r="I184" s="22"/>
+      <c r="J184" s="22"/>
+      <c r="K184" s="22"/>
+      <c r="L184" s="22"/>
+      <c r="M184" s="22"/>
+      <c r="N184" s="22"/>
+      <c r="O184" s="22"/>
+      <c r="P184" s="22"/>
+      <c r="Q184" s="22"/>
+      <c r="R184" s="22"/>
+      <c r="S184" s="22"/>
+      <c r="T184" s="22"/>
+      <c r="U184" s="22"/>
+      <c r="V184" s="22"/>
+      <c r="W184" s="22"/>
+      <c r="X184" s="22"/>
+      <c r="Y184" s="22"/>
+      <c r="Z184" s="23"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="9" t="s">
+      <c r="A185" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="B185" s="11" t="s">
+      <c r="B185" s="36" t="s">
         <v>312</v>
       </c>
-      <c r="C185" s="11" t="s">
+      <c r="C185" s="36" t="s">
+        <v>312</v>
+      </c>
+      <c r="D185" s="36"/>
+      <c r="E185" s="36"/>
+      <c r="F185" s="36"/>
+      <c r="G185" s="36"/>
+      <c r="H185" s="36"/>
+      <c r="I185" s="36"/>
+      <c r="J185" s="36"/>
+      <c r="K185" s="36"/>
+      <c r="L185" s="36"/>
+      <c r="M185" s="36"/>
+      <c r="N185" s="36"/>
+      <c r="O185" s="36"/>
+      <c r="P185" s="36"/>
+      <c r="Q185" s="36"/>
+      <c r="R185" s="36"/>
+      <c r="S185" s="36"/>
+      <c r="T185" s="36"/>
+      <c r="U185" s="36"/>
+      <c r="V185" s="36"/>
+      <c r="W185" s="36"/>
+      <c r="X185" s="36"/>
+      <c r="Y185" s="36"/>
+      <c r="Z185" s="37"/>
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
+      <c r="A186" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="D185" s="11"/>
-      <c r="E185" s="11"/>
-      <c r="F185" s="11"/>
-      <c r="G185" s="11"/>
-      <c r="H185" s="11"/>
-      <c r="I185" s="11"/>
-      <c r="J185" s="11"/>
-      <c r="K185" s="11"/>
-      <c r="L185" s="11"/>
-      <c r="M185" s="11"/>
-      <c r="N185" s="11"/>
-      <c r="O185" s="11"/>
-      <c r="P185" s="11"/>
-      <c r="Q185" s="11"/>
-      <c r="R185" s="11"/>
-      <c r="S185" s="11"/>
-      <c r="T185" s="11"/>
-      <c r="U185" s="11"/>
-      <c r="V185" s="11"/>
-      <c r="W185" s="11"/>
-      <c r="X185" s="11"/>
-      <c r="Y185" s="11"/>
-      <c r="Z185" s="12"/>
-    </row>
-    <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="15" t="s">
+      <c r="B186" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C186" s="1" t="s">
+      <c r="C186" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="D186" s="1"/>
-      <c r="E186" s="1"/>
-      <c r="F186" s="1"/>
-      <c r="G186" s="1"/>
-      <c r="H186" s="1"/>
-      <c r="I186" s="1"/>
-      <c r="J186" s="1"/>
-      <c r="K186" s="1"/>
-      <c r="L186" s="1"/>
-      <c r="M186" s="1"/>
-      <c r="N186" s="1"/>
-      <c r="O186" s="1"/>
-      <c r="P186" s="1"/>
-      <c r="Q186" s="1"/>
-      <c r="R186" s="1"/>
-      <c r="S186" s="1"/>
-      <c r="T186" s="1"/>
-      <c r="U186" s="1"/>
-      <c r="V186" s="1"/>
-      <c r="W186" s="1"/>
-      <c r="X186" s="1"/>
-      <c r="Y186" s="1"/>
-      <c r="Z186" s="14"/>
+      <c r="D186" s="11"/>
+      <c r="E186" s="11"/>
+      <c r="F186" s="11"/>
+      <c r="G186" s="11"/>
+      <c r="H186" s="11"/>
+      <c r="I186" s="11"/>
+      <c r="J186" s="11"/>
+      <c r="K186" s="11"/>
+      <c r="L186" s="11"/>
+      <c r="M186" s="11"/>
+      <c r="N186" s="11"/>
+      <c r="O186" s="11"/>
+      <c r="P186" s="11"/>
+      <c r="Q186" s="11"/>
+      <c r="R186" s="11"/>
+      <c r="S186" s="11"/>
+      <c r="T186" s="11"/>
+      <c r="U186" s="11"/>
+      <c r="V186" s="11"/>
+      <c r="W186" s="11"/>
+      <c r="X186" s="11"/>
+      <c r="Y186" s="11"/>
+      <c r="Z186" s="12"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="15" t="s">
         <v>316</v>
       </c>
       <c r="B187" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C187" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
@@ -7881,72 +7887,72 @@
       <c r="Z187" s="14"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="9" t="s">
+      <c r="A188" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B188" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="C188" s="11" t="s">
+      <c r="C188" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="D188" s="11"/>
-      <c r="E188" s="11"/>
-      <c r="F188" s="11"/>
-      <c r="G188" s="11"/>
-      <c r="H188" s="11"/>
-      <c r="I188" s="11"/>
-      <c r="J188" s="11"/>
-      <c r="K188" s="11"/>
-      <c r="L188" s="11"/>
-      <c r="M188" s="11"/>
-      <c r="N188" s="11"/>
-      <c r="O188" s="11"/>
-      <c r="P188" s="11"/>
-      <c r="Q188" s="11"/>
-      <c r="R188" s="11"/>
-      <c r="S188" s="11"/>
-      <c r="T188" s="11"/>
-      <c r="U188" s="11"/>
-      <c r="V188" s="11"/>
-      <c r="W188" s="11"/>
-      <c r="X188" s="11"/>
-      <c r="Y188" s="11"/>
-      <c r="Z188" s="12"/>
+      <c r="D188" s="1"/>
+      <c r="E188" s="1"/>
+      <c r="F188" s="1"/>
+      <c r="G188" s="1"/>
+      <c r="H188" s="1"/>
+      <c r="I188" s="1"/>
+      <c r="J188" s="1"/>
+      <c r="K188" s="1"/>
+      <c r="L188" s="1"/>
+      <c r="M188" s="1"/>
+      <c r="N188" s="1"/>
+      <c r="O188" s="1"/>
+      <c r="P188" s="1"/>
+      <c r="Q188" s="1"/>
+      <c r="R188" s="1"/>
+      <c r="S188" s="1"/>
+      <c r="T188" s="1"/>
+      <c r="U188" s="1"/>
+      <c r="V188" s="1"/>
+      <c r="W188" s="1"/>
+      <c r="X188" s="1"/>
+      <c r="Y188" s="1"/>
+      <c r="Z188" s="14"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="15" t="s">
+      <c r="A189" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="B189" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="C189" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="D189" s="1"/>
-      <c r="E189" s="1"/>
-      <c r="F189" s="1"/>
-      <c r="G189" s="1"/>
-      <c r="H189" s="1"/>
-      <c r="I189" s="1"/>
-      <c r="J189" s="1"/>
-      <c r="K189" s="1"/>
-      <c r="L189" s="1"/>
-      <c r="M189" s="1"/>
-      <c r="N189" s="1"/>
-      <c r="O189" s="1"/>
-      <c r="P189" s="1"/>
-      <c r="Q189" s="1"/>
-      <c r="R189" s="1"/>
-      <c r="S189" s="1"/>
-      <c r="T189" s="1"/>
-      <c r="U189" s="1"/>
-      <c r="V189" s="1"/>
-      <c r="W189" s="1"/>
-      <c r="X189" s="1"/>
-      <c r="Y189" s="1"/>
-      <c r="Z189" s="14"/>
+      <c r="D189" s="11"/>
+      <c r="E189" s="11"/>
+      <c r="F189" s="11"/>
+      <c r="G189" s="11"/>
+      <c r="H189" s="11"/>
+      <c r="I189" s="11"/>
+      <c r="J189" s="11"/>
+      <c r="K189" s="11"/>
+      <c r="L189" s="11"/>
+      <c r="M189" s="11"/>
+      <c r="N189" s="11"/>
+      <c r="O189" s="11"/>
+      <c r="P189" s="11"/>
+      <c r="Q189" s="11"/>
+      <c r="R189" s="11"/>
+      <c r="S189" s="11"/>
+      <c r="T189" s="11"/>
+      <c r="U189" s="11"/>
+      <c r="V189" s="11"/>
+      <c r="W189" s="11"/>
+      <c r="X189" s="11"/>
+      <c r="Y189" s="11"/>
+      <c r="Z189" s="12"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="15" t="s">
@@ -7983,130 +7989,130 @@
       <c r="Z190" s="14"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="18" t="s">
+      <c r="A191" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="B191" s="19" t="s">
+      <c r="B191" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C191" s="19" t="s">
+      <c r="C191" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="D191" s="19"/>
-      <c r="E191" s="19"/>
-      <c r="F191" s="19"/>
-      <c r="G191" s="19"/>
-      <c r="H191" s="19"/>
-      <c r="I191" s="19"/>
-      <c r="J191" s="19"/>
-      <c r="K191" s="19"/>
-      <c r="L191" s="19"/>
-      <c r="M191" s="19"/>
-      <c r="N191" s="19"/>
-      <c r="O191" s="19"/>
-      <c r="P191" s="19"/>
-      <c r="Q191" s="19"/>
-      <c r="R191" s="19"/>
-      <c r="S191" s="19"/>
-      <c r="T191" s="19"/>
-      <c r="U191" s="19"/>
-      <c r="V191" s="19"/>
-      <c r="W191" s="19"/>
-      <c r="X191" s="19"/>
-      <c r="Y191" s="19"/>
-      <c r="Z191" s="20"/>
+      <c r="D191" s="1"/>
+      <c r="E191" s="1"/>
+      <c r="F191" s="1"/>
+      <c r="G191" s="1"/>
+      <c r="H191" s="1"/>
+      <c r="I191" s="1"/>
+      <c r="J191" s="1"/>
+      <c r="K191" s="1"/>
+      <c r="L191" s="1"/>
+      <c r="M191" s="1"/>
+      <c r="N191" s="1"/>
+      <c r="O191" s="1"/>
+      <c r="P191" s="1"/>
+      <c r="Q191" s="1"/>
+      <c r="R191" s="1"/>
+      <c r="S191" s="1"/>
+      <c r="T191" s="1"/>
+      <c r="U191" s="1"/>
+      <c r="V191" s="1"/>
+      <c r="W191" s="1"/>
+      <c r="X191" s="1"/>
+      <c r="Y191" s="1"/>
+      <c r="Z191" s="14"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="1"/>
-      <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
-      <c r="E192" s="1"/>
-      <c r="F192" s="1"/>
-      <c r="G192" s="1"/>
-      <c r="H192" s="1"/>
-      <c r="I192" s="1"/>
-      <c r="J192" s="1"/>
-      <c r="K192" s="1"/>
-      <c r="L192" s="1"/>
-      <c r="M192" s="1"/>
-      <c r="N192" s="1"/>
-      <c r="O192" s="1"/>
-      <c r="P192" s="1"/>
-      <c r="Q192" s="1"/>
-      <c r="R192" s="1"/>
-      <c r="S192" s="1"/>
-      <c r="T192" s="1"/>
-      <c r="U192" s="1"/>
-      <c r="V192" s="1"/>
-      <c r="W192" s="1"/>
-      <c r="X192" s="1"/>
-      <c r="Y192" s="1"/>
-      <c r="Z192" s="1"/>
+      <c r="A192" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="B192" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="C192" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="D192" s="19"/>
+      <c r="E192" s="19"/>
+      <c r="F192" s="19"/>
+      <c r="G192" s="19"/>
+      <c r="H192" s="19"/>
+      <c r="I192" s="19"/>
+      <c r="J192" s="19"/>
+      <c r="K192" s="19"/>
+      <c r="L192" s="19"/>
+      <c r="M192" s="19"/>
+      <c r="N192" s="19"/>
+      <c r="O192" s="19"/>
+      <c r="P192" s="19"/>
+      <c r="Q192" s="19"/>
+      <c r="R192" s="19"/>
+      <c r="S192" s="19"/>
+      <c r="T192" s="19"/>
+      <c r="U192" s="19"/>
+      <c r="V192" s="19"/>
+      <c r="W192" s="19"/>
+      <c r="X192" s="19"/>
+      <c r="Y192" s="19"/>
+      <c r="Z192" s="20"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B193" s="2"/>
-      <c r="C193" s="2"/>
-      <c r="D193" s="2"/>
-      <c r="E193" s="2"/>
-      <c r="F193" s="2"/>
-      <c r="G193" s="2"/>
-      <c r="H193" s="2"/>
-      <c r="I193" s="2"/>
-      <c r="J193" s="2"/>
-      <c r="K193" s="2"/>
-      <c r="L193" s="2"/>
-      <c r="M193" s="2"/>
-      <c r="N193" s="2"/>
-      <c r="O193" s="2"/>
-      <c r="P193" s="2"/>
-      <c r="Q193" s="2"/>
-      <c r="R193" s="2"/>
-      <c r="S193" s="2"/>
-      <c r="T193" s="2"/>
-      <c r="U193" s="2"/>
-      <c r="V193" s="2"/>
-      <c r="W193" s="2"/>
-      <c r="X193" s="2"/>
-      <c r="Y193" s="2"/>
-      <c r="Z193" s="2"/>
+      <c r="A193" s="1"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
+      <c r="E193" s="1"/>
+      <c r="F193" s="1"/>
+      <c r="G193" s="1"/>
+      <c r="H193" s="1"/>
+      <c r="I193" s="1"/>
+      <c r="J193" s="1"/>
+      <c r="K193" s="1"/>
+      <c r="L193" s="1"/>
+      <c r="M193" s="1"/>
+      <c r="N193" s="1"/>
+      <c r="O193" s="1"/>
+      <c r="P193" s="1"/>
+      <c r="Q193" s="1"/>
+      <c r="R193" s="1"/>
+      <c r="S193" s="1"/>
+      <c r="T193" s="1"/>
+      <c r="U193" s="1"/>
+      <c r="V193" s="1"/>
+      <c r="W193" s="1"/>
+      <c r="X193" s="1"/>
+      <c r="Y193" s="1"/>
+      <c r="Z193" s="1"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C194" s="1" t="s">
+      <c r="A194" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D194" s="1"/>
-      <c r="E194" s="1"/>
-      <c r="F194" s="1"/>
-      <c r="G194" s="1"/>
-      <c r="H194" s="1"/>
-      <c r="I194" s="1"/>
-      <c r="J194" s="1"/>
-      <c r="K194" s="1"/>
-      <c r="L194" s="1"/>
-      <c r="M194" s="1"/>
-      <c r="N194" s="1"/>
-      <c r="O194" s="1"/>
-      <c r="P194" s="1"/>
-      <c r="Q194" s="1"/>
-      <c r="R194" s="1"/>
-      <c r="S194" s="1"/>
-      <c r="T194" s="1"/>
-      <c r="U194" s="1"/>
-      <c r="V194" s="1"/>
-      <c r="W194" s="1"/>
-      <c r="X194" s="1"/>
-      <c r="Y194" s="1"/>
-      <c r="Z194" s="1"/>
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
+      <c r="E194" s="2"/>
+      <c r="F194" s="2"/>
+      <c r="G194" s="2"/>
+      <c r="H194" s="2"/>
+      <c r="I194" s="2"/>
+      <c r="J194" s="2"/>
+      <c r="K194" s="2"/>
+      <c r="L194" s="2"/>
+      <c r="M194" s="2"/>
+      <c r="N194" s="2"/>
+      <c r="O194" s="2"/>
+      <c r="P194" s="2"/>
+      <c r="Q194" s="2"/>
+      <c r="R194" s="2"/>
+      <c r="S194" s="2"/>
+      <c r="T194" s="2"/>
+      <c r="U194" s="2"/>
+      <c r="V194" s="2"/>
+      <c r="W194" s="2"/>
+      <c r="X194" s="2"/>
+      <c r="Y194" s="2"/>
+      <c r="Z194" s="2"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="1" t="s">
@@ -8211,9 +8217,15 @@
       <c r="Z197" s="1"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="1"/>
-      <c r="B198" s="1"/>
-      <c r="C198" s="1"/>
+      <c r="A198" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>337</v>
+      </c>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
@@ -8239,73 +8251,73 @@
       <c r="Z198" s="1"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B199" s="2"/>
-      <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
-      <c r="E199" s="2"/>
-      <c r="F199" s="2"/>
-      <c r="G199" s="2"/>
-      <c r="H199" s="2"/>
-      <c r="I199" s="2"/>
-      <c r="J199" s="2"/>
-      <c r="K199" s="2"/>
-      <c r="L199" s="2"/>
-      <c r="M199" s="2"/>
-      <c r="N199" s="2"/>
-      <c r="O199" s="2"/>
-      <c r="P199" s="2"/>
-      <c r="Q199" s="2"/>
-      <c r="R199" s="2"/>
-      <c r="S199" s="2"/>
-      <c r="T199" s="2"/>
-      <c r="U199" s="2"/>
-      <c r="V199" s="2"/>
-      <c r="W199" s="2"/>
-      <c r="X199" s="2"/>
-      <c r="Y199" s="2"/>
-      <c r="Z199" s="2"/>
+      <c r="A199" s="1"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
+      <c r="E199" s="1"/>
+      <c r="F199" s="1"/>
+      <c r="G199" s="1"/>
+      <c r="H199" s="1"/>
+      <c r="I199" s="1"/>
+      <c r="J199" s="1"/>
+      <c r="K199" s="1"/>
+      <c r="L199" s="1"/>
+      <c r="M199" s="1"/>
+      <c r="N199" s="1"/>
+      <c r="O199" s="1"/>
+      <c r="P199" s="1"/>
+      <c r="Q199" s="1"/>
+      <c r="R199" s="1"/>
+      <c r="S199" s="1"/>
+      <c r="T199" s="1"/>
+      <c r="U199" s="1"/>
+      <c r="V199" s="1"/>
+      <c r="W199" s="1"/>
+      <c r="X199" s="1"/>
+      <c r="Y199" s="1"/>
+      <c r="Z199" s="1"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C200" s="1" t="s">
+      <c r="A200" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="D200" s="1"/>
-      <c r="E200" s="1"/>
-      <c r="F200" s="1"/>
-      <c r="G200" s="1"/>
-      <c r="H200" s="1"/>
-      <c r="I200" s="1"/>
-      <c r="J200" s="1"/>
-      <c r="K200" s="1"/>
-      <c r="L200" s="1"/>
-      <c r="M200" s="1"/>
-      <c r="N200" s="1"/>
-      <c r="O200" s="1"/>
-      <c r="P200" s="1"/>
-      <c r="Q200" s="1"/>
-      <c r="R200" s="1"/>
-      <c r="S200" s="1"/>
-      <c r="T200" s="1"/>
-      <c r="U200" s="1"/>
-      <c r="V200" s="1"/>
-      <c r="W200" s="1"/>
-      <c r="X200" s="1"/>
-      <c r="Y200" s="1"/>
-      <c r="Z200" s="1"/>
+      <c r="B200" s="2"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
+      <c r="E200" s="2"/>
+      <c r="F200" s="2"/>
+      <c r="G200" s="2"/>
+      <c r="H200" s="2"/>
+      <c r="I200" s="2"/>
+      <c r="J200" s="2"/>
+      <c r="K200" s="2"/>
+      <c r="L200" s="2"/>
+      <c r="M200" s="2"/>
+      <c r="N200" s="2"/>
+      <c r="O200" s="2"/>
+      <c r="P200" s="2"/>
+      <c r="Q200" s="2"/>
+      <c r="R200" s="2"/>
+      <c r="S200" s="2"/>
+      <c r="T200" s="2"/>
+      <c r="U200" s="2"/>
+      <c r="V200" s="2"/>
+      <c r="W200" s="2"/>
+      <c r="X200" s="2"/>
+      <c r="Y200" s="2"/>
+      <c r="Z200" s="2"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="1"/>
-      <c r="B201" s="1"/>
-      <c r="C201" s="1"/>
+      <c r="A201" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>340</v>
+      </c>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
@@ -8331,78 +8343,72 @@
       <c r="Z201" s="1"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B202" s="2"/>
-      <c r="C202" s="2"/>
-      <c r="D202" s="2"/>
-      <c r="E202" s="2"/>
-      <c r="F202" s="2"/>
-      <c r="G202" s="2"/>
-      <c r="H202" s="2"/>
-      <c r="I202" s="2"/>
-      <c r="J202" s="2"/>
-      <c r="K202" s="2"/>
-      <c r="L202" s="2"/>
-      <c r="M202" s="2"/>
-      <c r="N202" s="2"/>
-      <c r="O202" s="2"/>
-      <c r="P202" s="2"/>
-      <c r="Q202" s="2"/>
-      <c r="R202" s="2"/>
-      <c r="S202" s="2"/>
-      <c r="T202" s="2"/>
-      <c r="U202" s="2"/>
-      <c r="V202" s="2"/>
-      <c r="W202" s="2"/>
-      <c r="X202" s="2"/>
-      <c r="Y202" s="2"/>
-      <c r="Z202" s="2"/>
+      <c r="A202" s="1"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
+      <c r="E202" s="1"/>
+      <c r="F202" s="1"/>
+      <c r="G202" s="1"/>
+      <c r="H202" s="1"/>
+      <c r="I202" s="1"/>
+      <c r="J202" s="1"/>
+      <c r="K202" s="1"/>
+      <c r="L202" s="1"/>
+      <c r="M202" s="1"/>
+      <c r="N202" s="1"/>
+      <c r="O202" s="1"/>
+      <c r="P202" s="1"/>
+      <c r="Q202" s="1"/>
+      <c r="R202" s="1"/>
+      <c r="S202" s="1"/>
+      <c r="T202" s="1"/>
+      <c r="U202" s="1"/>
+      <c r="V202" s="1"/>
+      <c r="W202" s="1"/>
+      <c r="X202" s="1"/>
+      <c r="Y202" s="1"/>
+      <c r="Z202" s="1"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B203" s="1" t="s">
+      <c r="A203" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C203" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D203" s="1"/>
-      <c r="E203" s="1"/>
-      <c r="F203" s="1"/>
-      <c r="G203" s="1"/>
-      <c r="H203" s="1"/>
-      <c r="I203" s="1"/>
-      <c r="J203" s="1"/>
-      <c r="K203" s="1"/>
-      <c r="L203" s="1"/>
-      <c r="M203" s="1"/>
-      <c r="N203" s="1"/>
-      <c r="O203" s="1"/>
-      <c r="P203" s="1"/>
-      <c r="Q203" s="1"/>
-      <c r="R203" s="1"/>
-      <c r="S203" s="1"/>
-      <c r="T203" s="1"/>
-      <c r="U203" s="1"/>
-      <c r="V203" s="1"/>
-      <c r="W203" s="1"/>
-      <c r="X203" s="1"/>
-      <c r="Y203" s="1"/>
-      <c r="Z203" s="1"/>
+      <c r="B203" s="2"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
+      <c r="E203" s="2"/>
+      <c r="F203" s="2"/>
+      <c r="G203" s="2"/>
+      <c r="H203" s="2"/>
+      <c r="I203" s="2"/>
+      <c r="J203" s="2"/>
+      <c r="K203" s="2"/>
+      <c r="L203" s="2"/>
+      <c r="M203" s="2"/>
+      <c r="N203" s="2"/>
+      <c r="O203" s="2"/>
+      <c r="P203" s="2"/>
+      <c r="Q203" s="2"/>
+      <c r="R203" s="2"/>
+      <c r="S203" s="2"/>
+      <c r="T203" s="2"/>
+      <c r="U203" s="2"/>
+      <c r="V203" s="2"/>
+      <c r="W203" s="2"/>
+      <c r="X203" s="2"/>
+      <c r="Y203" s="2"/>
+      <c r="Z203" s="2"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="C204" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
@@ -8430,13 +8436,13 @@
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="C205" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
@@ -8464,13 +8470,13 @@
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="C206" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
@@ -8498,7 +8504,7 @@
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>352</v>
@@ -8569,10 +8575,10 @@
         <v>356</v>
       </c>
       <c r="B209" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C209" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
@@ -8600,13 +8606,13 @@
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="C210" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
@@ -8634,13 +8640,13 @@
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B211" s="1" t="s">
+      <c r="C211" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
@@ -8668,13 +8674,13 @@
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="C212" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
@@ -8701,9 +8707,15 @@
       <c r="Z212" s="1"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="1"/>
-      <c r="B213" s="1"/>
-      <c r="C213" s="1"/>
+      <c r="A213" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>369</v>
+      </c>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
@@ -8729,78 +8741,72 @@
       <c r="Z213" s="1"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B214" s="2"/>
-      <c r="C214" s="2"/>
-      <c r="D214" s="2"/>
-      <c r="E214" s="2"/>
-      <c r="F214" s="2"/>
-      <c r="G214" s="2"/>
-      <c r="H214" s="2"/>
-      <c r="I214" s="2"/>
-      <c r="J214" s="2"/>
-      <c r="K214" s="2"/>
-      <c r="L214" s="2"/>
-      <c r="M214" s="2"/>
-      <c r="N214" s="2"/>
-      <c r="O214" s="2"/>
-      <c r="P214" s="2"/>
-      <c r="Q214" s="2"/>
-      <c r="R214" s="2"/>
-      <c r="S214" s="2"/>
-      <c r="T214" s="2"/>
-      <c r="U214" s="2"/>
-      <c r="V214" s="2"/>
-      <c r="W214" s="2"/>
-      <c r="X214" s="2"/>
-      <c r="Y214" s="2"/>
-      <c r="Z214" s="2"/>
+      <c r="A214" s="1"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
+      <c r="E214" s="1"/>
+      <c r="F214" s="1"/>
+      <c r="G214" s="1"/>
+      <c r="H214" s="1"/>
+      <c r="I214" s="1"/>
+      <c r="J214" s="1"/>
+      <c r="K214" s="1"/>
+      <c r="L214" s="1"/>
+      <c r="M214" s="1"/>
+      <c r="N214" s="1"/>
+      <c r="O214" s="1"/>
+      <c r="P214" s="1"/>
+      <c r="Q214" s="1"/>
+      <c r="R214" s="1"/>
+      <c r="S214" s="1"/>
+      <c r="T214" s="1"/>
+      <c r="U214" s="1"/>
+      <c r="V214" s="1"/>
+      <c r="W214" s="1"/>
+      <c r="X214" s="1"/>
+      <c r="Y214" s="1"/>
+      <c r="Z214" s="1"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D215" s="1"/>
-      <c r="E215" s="1"/>
-      <c r="F215" s="1"/>
-      <c r="G215" s="1"/>
-      <c r="H215" s="1"/>
-      <c r="I215" s="1"/>
-      <c r="J215" s="1"/>
-      <c r="K215" s="1"/>
-      <c r="L215" s="1"/>
-      <c r="M215" s="1"/>
-      <c r="N215" s="1"/>
-      <c r="O215" s="1"/>
-      <c r="P215" s="1"/>
-      <c r="Q215" s="1"/>
-      <c r="R215" s="1"/>
-      <c r="S215" s="1"/>
-      <c r="T215" s="1"/>
-      <c r="U215" s="1"/>
-      <c r="V215" s="1"/>
-      <c r="W215" s="1"/>
-      <c r="X215" s="1"/>
-      <c r="Y215" s="1"/>
-      <c r="Z215" s="1"/>
+      <c r="A215" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+      <c r="E215" s="2"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
+      <c r="J215" s="2"/>
+      <c r="K215" s="2"/>
+      <c r="L215" s="2"/>
+      <c r="M215" s="2"/>
+      <c r="N215" s="2"/>
+      <c r="O215" s="2"/>
+      <c r="P215" s="2"/>
+      <c r="Q215" s="2"/>
+      <c r="R215" s="2"/>
+      <c r="S215" s="2"/>
+      <c r="T215" s="2"/>
+      <c r="U215" s="2"/>
+      <c r="V215" s="2"/>
+      <c r="W215" s="2"/>
+      <c r="X215" s="2"/>
+      <c r="Y215" s="2"/>
+      <c r="Z215" s="2"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="C216" s="38" t="s">
-        <v>66</v>
+      <c r="C216" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -8831,9 +8837,9 @@
         <v>371</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="C217" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C217" s="38" t="s">
         <v>66</v>
       </c>
       <c r="D217" s="1"/>
@@ -8862,13 +8868,13 @@
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>373</v>
+        <v>66</v>
       </c>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
@@ -8935,7 +8941,7 @@
       <c r="B220" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C220" s="38" t="s">
+      <c r="C220" s="1" t="s">
         <v>377</v>
       </c>
       <c r="D220" s="1"/>
@@ -8970,7 +8976,7 @@
         <v>378</v>
       </c>
       <c r="C221" s="38" t="s">
-        <v>20</v>
+        <v>379</v>
       </c>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
@@ -8998,13 +9004,13 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>16</v>
+        <v>380</v>
+      </c>
+      <c r="C222" s="38" t="s">
+        <v>20</v>
       </c>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
@@ -9032,13 +9038,13 @@
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
@@ -9066,13 +9072,13 @@
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>382</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>383</v>
+        <v>18</v>
       </c>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
@@ -9100,13 +9106,13 @@
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B225" s="1" t="s">
+      <c r="C225" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="C225" s="38" t="s">
-        <v>386</v>
       </c>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
@@ -9134,13 +9140,13 @@
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B226" s="1" t="s">
+      <c r="C226" s="38" t="s">
         <v>388</v>
-      </c>
-      <c r="C226" s="38" t="s">
-        <v>389</v>
       </c>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
@@ -9167,9 +9173,15 @@
       <c r="Z226" s="1"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="1"/>
-      <c r="B227" s="1"/>
-      <c r="C227" s="1"/>
+      <c r="A227" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C227" s="38" t="s">
+        <v>391</v>
+      </c>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
@@ -14767,32 +14779,32 @@
       <c r="Z426" s="1"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="21"/>
-      <c r="B427" s="21"/>
-      <c r="C427" s="21"/>
-      <c r="D427" s="21"/>
-      <c r="E427" s="21"/>
-      <c r="F427" s="21"/>
-      <c r="G427" s="21"/>
-      <c r="H427" s="21"/>
-      <c r="I427" s="21"/>
-      <c r="J427" s="21"/>
-      <c r="K427" s="21"/>
-      <c r="L427" s="21"/>
-      <c r="M427" s="21"/>
-      <c r="N427" s="21"/>
-      <c r="O427" s="21"/>
-      <c r="P427" s="21"/>
-      <c r="Q427" s="21"/>
-      <c r="R427" s="21"/>
-      <c r="S427" s="21"/>
-      <c r="T427" s="21"/>
-      <c r="U427" s="21"/>
-      <c r="V427" s="21"/>
-      <c r="W427" s="21"/>
-      <c r="X427" s="21"/>
-      <c r="Y427" s="21"/>
-      <c r="Z427" s="21"/>
+      <c r="A427" s="1"/>
+      <c r="B427" s="1"/>
+      <c r="C427" s="1"/>
+      <c r="D427" s="1"/>
+      <c r="E427" s="1"/>
+      <c r="F427" s="1"/>
+      <c r="G427" s="1"/>
+      <c r="H427" s="1"/>
+      <c r="I427" s="1"/>
+      <c r="J427" s="1"/>
+      <c r="K427" s="1"/>
+      <c r="L427" s="1"/>
+      <c r="M427" s="1"/>
+      <c r="N427" s="1"/>
+      <c r="O427" s="1"/>
+      <c r="P427" s="1"/>
+      <c r="Q427" s="1"/>
+      <c r="R427" s="1"/>
+      <c r="S427" s="1"/>
+      <c r="T427" s="1"/>
+      <c r="U427" s="1"/>
+      <c r="V427" s="1"/>
+      <c r="W427" s="1"/>
+      <c r="X427" s="1"/>
+      <c r="Y427" s="1"/>
+      <c r="Z427" s="1"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="21"/>
@@ -31454,6 +31466,34 @@
       <c r="Y1022" s="21"/>
       <c r="Z1022" s="21"/>
     </row>
+    <row r="1023" ht="15.75" customHeight="1">
+      <c r="A1023" s="21"/>
+      <c r="B1023" s="21"/>
+      <c r="C1023" s="21"/>
+      <c r="D1023" s="21"/>
+      <c r="E1023" s="21"/>
+      <c r="F1023" s="21"/>
+      <c r="G1023" s="21"/>
+      <c r="H1023" s="21"/>
+      <c r="I1023" s="21"/>
+      <c r="J1023" s="21"/>
+      <c r="K1023" s="21"/>
+      <c r="L1023" s="21"/>
+      <c r="M1023" s="21"/>
+      <c r="N1023" s="21"/>
+      <c r="O1023" s="21"/>
+      <c r="P1023" s="21"/>
+      <c r="Q1023" s="21"/>
+      <c r="R1023" s="21"/>
+      <c r="S1023" s="21"/>
+      <c r="T1023" s="21"/>
+      <c r="U1023" s="21"/>
+      <c r="V1023" s="21"/>
+      <c r="W1023" s="21"/>
+      <c r="X1023" s="21"/>
+      <c r="Y1023" s="21"/>
+      <c r="Z1023" s="21"/>
+    </row>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/Kooco_TexasHoldem/Assets/Resources/Language/Language.xlsx
+++ b/Kooco_TexasHoldem/Assets/Resources/Language/Language.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="bBIO3Tz9O17USJO/wvacB8QUctx0Qb1yMEY7DXzGXh0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="bCpl2ulkJwefW6eYTXpN2nVgNQ98B5sOQ0I0RcPB1AQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="421">
   <si>
     <t>ID</t>
   </si>
@@ -1044,6 +1044,12 @@
     <t>加注</t>
   </si>
   <si>
+    <t>Bet</t>
+  </si>
+  <si>
+    <t>下注</t>
+  </si>
+  <si>
     <t>Call</t>
   </si>
   <si>
@@ -1069,6 +1075,12 @@
   </si>
   <si>
     <t>加注至</t>
+  </si>
+  <si>
+    <t>BetTo</t>
+  </si>
+  <si>
+    <t>下注至</t>
   </si>
   <si>
     <t>CheckOrFold</t>
@@ -1303,7 +1315,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1323,6 +1335,10 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -1438,7 +1454,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1493,14 +1509,9 @@
     <xf borderId="6" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -1509,9 +1520,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
@@ -4299,10 +4322,10 @@
       <c r="A77" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B77" s="21" t="s">
+      <c r="B77" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C77" s="21" t="s">
+      <c r="C77" s="3" t="s">
         <v>141</v>
       </c>
       <c r="D77" s="3"/>
@@ -4330,13 +4353,13 @@
       <c r="Z77" s="3"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="22" t="s">
+      <c r="A78" s="21" t="s">
         <v>142</v>
       </c>
       <c r="B78" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="C78" s="21" t="s">
+      <c r="C78" s="3" t="s">
         <v>143</v>
       </c>
       <c r="D78" s="3"/>
@@ -5028,34 +5051,34 @@
       <c r="Z98" s="3"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="23" t="s">
+      <c r="A99" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="B99" s="23"/>
-      <c r="C99" s="23"/>
-      <c r="D99" s="23"/>
-      <c r="E99" s="23"/>
-      <c r="F99" s="23"/>
-      <c r="G99" s="23"/>
-      <c r="H99" s="23"/>
-      <c r="I99" s="23"/>
-      <c r="J99" s="23"/>
-      <c r="K99" s="23"/>
-      <c r="L99" s="23"/>
-      <c r="M99" s="23"/>
-      <c r="N99" s="23"/>
-      <c r="O99" s="23"/>
-      <c r="P99" s="23"/>
-      <c r="Q99" s="23"/>
-      <c r="R99" s="23"/>
-      <c r="S99" s="23"/>
-      <c r="T99" s="23"/>
-      <c r="U99" s="23"/>
-      <c r="V99" s="23"/>
-      <c r="W99" s="23"/>
-      <c r="X99" s="23"/>
-      <c r="Y99" s="23"/>
-      <c r="Z99" s="23"/>
+      <c r="B99" s="22"/>
+      <c r="C99" s="22"/>
+      <c r="D99" s="22"/>
+      <c r="E99" s="22"/>
+      <c r="F99" s="22"/>
+      <c r="G99" s="22"/>
+      <c r="H99" s="22"/>
+      <c r="I99" s="22"/>
+      <c r="J99" s="22"/>
+      <c r="K99" s="22"/>
+      <c r="L99" s="22"/>
+      <c r="M99" s="22"/>
+      <c r="N99" s="22"/>
+      <c r="O99" s="22"/>
+      <c r="P99" s="22"/>
+      <c r="Q99" s="22"/>
+      <c r="R99" s="22"/>
+      <c r="S99" s="22"/>
+      <c r="T99" s="22"/>
+      <c r="U99" s="22"/>
+      <c r="V99" s="22"/>
+      <c r="W99" s="22"/>
+      <c r="X99" s="22"/>
+      <c r="Y99" s="22"/>
+      <c r="Z99" s="22"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="3" t="s">
@@ -5160,34 +5183,34 @@
       <c r="Z102" s="3"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="23" t="s">
+      <c r="A103" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B103" s="23"/>
-      <c r="C103" s="23"/>
-      <c r="D103" s="23"/>
-      <c r="E103" s="23"/>
-      <c r="F103" s="23"/>
-      <c r="G103" s="23"/>
-      <c r="H103" s="23"/>
-      <c r="I103" s="23"/>
-      <c r="J103" s="23"/>
-      <c r="K103" s="23"/>
-      <c r="L103" s="23"/>
-      <c r="M103" s="23"/>
-      <c r="N103" s="23"/>
-      <c r="O103" s="23"/>
-      <c r="P103" s="23"/>
-      <c r="Q103" s="23"/>
-      <c r="R103" s="23"/>
-      <c r="S103" s="23"/>
-      <c r="T103" s="23"/>
-      <c r="U103" s="23"/>
-      <c r="V103" s="23"/>
-      <c r="W103" s="23"/>
-      <c r="X103" s="23"/>
-      <c r="Y103" s="23"/>
-      <c r="Z103" s="23"/>
+      <c r="B103" s="22"/>
+      <c r="C103" s="22"/>
+      <c r="D103" s="22"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="22"/>
+      <c r="G103" s="22"/>
+      <c r="H103" s="22"/>
+      <c r="I103" s="22"/>
+      <c r="J103" s="22"/>
+      <c r="K103" s="22"/>
+      <c r="L103" s="22"/>
+      <c r="M103" s="22"/>
+      <c r="N103" s="22"/>
+      <c r="O103" s="22"/>
+      <c r="P103" s="22"/>
+      <c r="Q103" s="22"/>
+      <c r="R103" s="22"/>
+      <c r="S103" s="22"/>
+      <c r="T103" s="22"/>
+      <c r="U103" s="22"/>
+      <c r="V103" s="22"/>
+      <c r="W103" s="22"/>
+      <c r="X103" s="22"/>
+      <c r="Y103" s="22"/>
+      <c r="Z103" s="22"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="3" t="s">
@@ -5326,34 +5349,34 @@
       <c r="Z107" s="3"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="24" t="s">
+      <c r="A108" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="B108" s="24"/>
-      <c r="C108" s="24"/>
-      <c r="D108" s="24"/>
-      <c r="E108" s="24"/>
-      <c r="F108" s="24"/>
-      <c r="G108" s="24"/>
-      <c r="H108" s="24"/>
-      <c r="I108" s="24"/>
-      <c r="J108" s="24"/>
-      <c r="K108" s="24"/>
-      <c r="L108" s="24"/>
-      <c r="M108" s="24"/>
-      <c r="N108" s="24"/>
-      <c r="O108" s="24"/>
-      <c r="P108" s="24"/>
-      <c r="Q108" s="24"/>
-      <c r="R108" s="24"/>
-      <c r="S108" s="24"/>
-      <c r="T108" s="24"/>
-      <c r="U108" s="24"/>
-      <c r="V108" s="24"/>
-      <c r="W108" s="24"/>
-      <c r="X108" s="24"/>
-      <c r="Y108" s="24"/>
-      <c r="Z108" s="24"/>
+      <c r="B108" s="23"/>
+      <c r="C108" s="23"/>
+      <c r="D108" s="23"/>
+      <c r="E108" s="23"/>
+      <c r="F108" s="23"/>
+      <c r="G108" s="23"/>
+      <c r="H108" s="23"/>
+      <c r="I108" s="23"/>
+      <c r="J108" s="23"/>
+      <c r="K108" s="23"/>
+      <c r="L108" s="23"/>
+      <c r="M108" s="23"/>
+      <c r="N108" s="23"/>
+      <c r="O108" s="23"/>
+      <c r="P108" s="23"/>
+      <c r="Q108" s="23"/>
+      <c r="R108" s="23"/>
+      <c r="S108" s="23"/>
+      <c r="T108" s="23"/>
+      <c r="U108" s="23"/>
+      <c r="V108" s="23"/>
+      <c r="W108" s="23"/>
+      <c r="X108" s="23"/>
+      <c r="Y108" s="23"/>
+      <c r="Z108" s="23"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="3" t="s">
@@ -5390,34 +5413,34 @@
       <c r="Z109" s="3"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="23" t="s">
+      <c r="A110" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="B110" s="23"/>
-      <c r="C110" s="23"/>
-      <c r="D110" s="23"/>
-      <c r="E110" s="23"/>
-      <c r="F110" s="23"/>
-      <c r="G110" s="23"/>
-      <c r="H110" s="23"/>
-      <c r="I110" s="23"/>
-      <c r="J110" s="23"/>
-      <c r="K110" s="23"/>
-      <c r="L110" s="23"/>
-      <c r="M110" s="23"/>
-      <c r="N110" s="23"/>
-      <c r="O110" s="23"/>
-      <c r="P110" s="23"/>
-      <c r="Q110" s="23"/>
-      <c r="R110" s="23"/>
-      <c r="S110" s="23"/>
-      <c r="T110" s="23"/>
-      <c r="U110" s="23"/>
-      <c r="V110" s="23"/>
-      <c r="W110" s="23"/>
-      <c r="X110" s="23"/>
-      <c r="Y110" s="23"/>
-      <c r="Z110" s="23"/>
+      <c r="B110" s="22"/>
+      <c r="C110" s="22"/>
+      <c r="D110" s="22"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="22"/>
+      <c r="G110" s="22"/>
+      <c r="H110" s="22"/>
+      <c r="I110" s="22"/>
+      <c r="J110" s="22"/>
+      <c r="K110" s="22"/>
+      <c r="L110" s="22"/>
+      <c r="M110" s="22"/>
+      <c r="N110" s="22"/>
+      <c r="O110" s="22"/>
+      <c r="P110" s="22"/>
+      <c r="Q110" s="22"/>
+      <c r="R110" s="22"/>
+      <c r="S110" s="22"/>
+      <c r="T110" s="22"/>
+      <c r="U110" s="22"/>
+      <c r="V110" s="22"/>
+      <c r="W110" s="22"/>
+      <c r="X110" s="22"/>
+      <c r="Y110" s="22"/>
+      <c r="Z110" s="22"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="3" t="s">
@@ -5522,34 +5545,34 @@
       <c r="Z113" s="3"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="23" t="s">
+      <c r="A114" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B114" s="23"/>
-      <c r="C114" s="23"/>
-      <c r="D114" s="23"/>
-      <c r="E114" s="23"/>
-      <c r="F114" s="23"/>
-      <c r="G114" s="23"/>
-      <c r="H114" s="23"/>
-      <c r="I114" s="23"/>
-      <c r="J114" s="23"/>
-      <c r="K114" s="23"/>
-      <c r="L114" s="23"/>
-      <c r="M114" s="23"/>
-      <c r="N114" s="23"/>
-      <c r="O114" s="23"/>
-      <c r="P114" s="23"/>
-      <c r="Q114" s="23"/>
-      <c r="R114" s="23"/>
-      <c r="S114" s="23"/>
-      <c r="T114" s="23"/>
-      <c r="U114" s="23"/>
-      <c r="V114" s="23"/>
-      <c r="W114" s="23"/>
-      <c r="X114" s="23"/>
-      <c r="Y114" s="23"/>
-      <c r="Z114" s="23"/>
+      <c r="B114" s="22"/>
+      <c r="C114" s="22"/>
+      <c r="D114" s="22"/>
+      <c r="E114" s="22"/>
+      <c r="F114" s="22"/>
+      <c r="G114" s="22"/>
+      <c r="H114" s="22"/>
+      <c r="I114" s="22"/>
+      <c r="J114" s="22"/>
+      <c r="K114" s="22"/>
+      <c r="L114" s="22"/>
+      <c r="M114" s="22"/>
+      <c r="N114" s="22"/>
+      <c r="O114" s="22"/>
+      <c r="P114" s="22"/>
+      <c r="Q114" s="22"/>
+      <c r="R114" s="22"/>
+      <c r="S114" s="22"/>
+      <c r="T114" s="22"/>
+      <c r="U114" s="22"/>
+      <c r="V114" s="22"/>
+      <c r="W114" s="22"/>
+      <c r="X114" s="22"/>
+      <c r="Y114" s="22"/>
+      <c r="Z114" s="22"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="1" t="s">
@@ -5586,34 +5609,34 @@
       <c r="Z115" s="1"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="23" t="s">
+      <c r="A116" s="22" t="s">
         <v>208</v>
       </c>
-      <c r="B116" s="23"/>
-      <c r="C116" s="23"/>
-      <c r="D116" s="23"/>
-      <c r="E116" s="23"/>
-      <c r="F116" s="23"/>
-      <c r="G116" s="23"/>
-      <c r="H116" s="23"/>
-      <c r="I116" s="23"/>
-      <c r="J116" s="23"/>
-      <c r="K116" s="23"/>
-      <c r="L116" s="23"/>
-      <c r="M116" s="23"/>
-      <c r="N116" s="23"/>
-      <c r="O116" s="23"/>
-      <c r="P116" s="23"/>
-      <c r="Q116" s="23"/>
-      <c r="R116" s="23"/>
-      <c r="S116" s="23"/>
-      <c r="T116" s="23"/>
-      <c r="U116" s="23"/>
-      <c r="V116" s="23"/>
-      <c r="W116" s="23"/>
-      <c r="X116" s="23"/>
-      <c r="Y116" s="23"/>
-      <c r="Z116" s="23"/>
+      <c r="B116" s="22"/>
+      <c r="C116" s="22"/>
+      <c r="D116" s="22"/>
+      <c r="E116" s="22"/>
+      <c r="F116" s="22"/>
+      <c r="G116" s="22"/>
+      <c r="H116" s="22"/>
+      <c r="I116" s="22"/>
+      <c r="J116" s="22"/>
+      <c r="K116" s="22"/>
+      <c r="L116" s="22"/>
+      <c r="M116" s="22"/>
+      <c r="N116" s="22"/>
+      <c r="O116" s="22"/>
+      <c r="P116" s="22"/>
+      <c r="Q116" s="22"/>
+      <c r="R116" s="22"/>
+      <c r="S116" s="22"/>
+      <c r="T116" s="22"/>
+      <c r="U116" s="22"/>
+      <c r="V116" s="22"/>
+      <c r="W116" s="22"/>
+      <c r="X116" s="22"/>
+      <c r="Y116" s="22"/>
+      <c r="Z116" s="22"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="4" t="s">
@@ -6664,7 +6687,7 @@
       <c r="Z148" s="10"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="25" t="s">
+      <c r="A149" s="24" t="s">
         <v>258</v>
       </c>
       <c r="B149" s="1" t="s">
@@ -8008,7 +8031,7 @@
       <c r="Z189" s="10"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="25" t="s">
+      <c r="A190" s="24" t="s">
         <v>326</v>
       </c>
       <c r="B190" s="17" t="s">
@@ -8042,7 +8065,7 @@
       <c r="Z190" s="18"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="25" t="s">
+      <c r="A191" s="24" t="s">
         <v>328</v>
       </c>
       <c r="B191" s="17" t="s">
@@ -8076,7 +8099,7 @@
       <c r="Z191" s="18"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="25" t="s">
+      <c r="A192" s="24" t="s">
         <v>330</v>
       </c>
       <c r="B192" s="17" t="s">
@@ -8113,10 +8136,10 @@
       <c r="A193" s="25" t="s">
         <v>332</v>
       </c>
-      <c r="B193" s="17" t="s">
+      <c r="B193" s="26" t="s">
         <v>332</v>
       </c>
-      <c r="C193" s="17" t="s">
+      <c r="C193" s="26" t="s">
         <v>333</v>
       </c>
       <c r="D193" s="17"/>
@@ -8144,116 +8167,116 @@
       <c r="Z193" s="18"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="26" t="s">
+      <c r="A194" s="24" t="s">
         <v>334</v>
       </c>
-      <c r="B194" s="27" t="s">
+      <c r="B194" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="C194" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="C194" s="27" t="s">
-        <v>335</v>
-      </c>
-      <c r="D194" s="27"/>
-      <c r="E194" s="27"/>
-      <c r="F194" s="27"/>
-      <c r="G194" s="27"/>
-      <c r="H194" s="27"/>
-      <c r="I194" s="27"/>
-      <c r="J194" s="27"/>
-      <c r="K194" s="27"/>
-      <c r="L194" s="27"/>
-      <c r="M194" s="27"/>
-      <c r="N194" s="27"/>
-      <c r="O194" s="27"/>
-      <c r="P194" s="27"/>
-      <c r="Q194" s="27"/>
-      <c r="R194" s="27"/>
-      <c r="S194" s="27"/>
-      <c r="T194" s="27"/>
-      <c r="U194" s="27"/>
-      <c r="V194" s="27"/>
-      <c r="W194" s="27"/>
-      <c r="X194" s="27"/>
-      <c r="Y194" s="27"/>
-      <c r="Z194" s="28"/>
+      <c r="D194" s="17"/>
+      <c r="E194" s="17"/>
+      <c r="F194" s="17"/>
+      <c r="G194" s="17"/>
+      <c r="H194" s="17"/>
+      <c r="I194" s="17"/>
+      <c r="J194" s="17"/>
+      <c r="K194" s="17"/>
+      <c r="L194" s="17"/>
+      <c r="M194" s="17"/>
+      <c r="N194" s="17"/>
+      <c r="O194" s="17"/>
+      <c r="P194" s="17"/>
+      <c r="Q194" s="17"/>
+      <c r="R194" s="17"/>
+      <c r="S194" s="17"/>
+      <c r="T194" s="17"/>
+      <c r="U194" s="17"/>
+      <c r="V194" s="17"/>
+      <c r="W194" s="17"/>
+      <c r="X194" s="17"/>
+      <c r="Y194" s="17"/>
+      <c r="Z194" s="18"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="7" t="s">
+      <c r="A195" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="B195" s="9" t="s">
+      <c r="B195" s="28" t="s">
         <v>337</v>
       </c>
-      <c r="C195" s="9" t="s">
+      <c r="C195" s="28" t="s">
+        <v>337</v>
+      </c>
+      <c r="D195" s="28"/>
+      <c r="E195" s="28"/>
+      <c r="F195" s="28"/>
+      <c r="G195" s="28"/>
+      <c r="H195" s="28"/>
+      <c r="I195" s="28"/>
+      <c r="J195" s="28"/>
+      <c r="K195" s="28"/>
+      <c r="L195" s="28"/>
+      <c r="M195" s="28"/>
+      <c r="N195" s="28"/>
+      <c r="O195" s="28"/>
+      <c r="P195" s="28"/>
+      <c r="Q195" s="28"/>
+      <c r="R195" s="28"/>
+      <c r="S195" s="28"/>
+      <c r="T195" s="28"/>
+      <c r="U195" s="28"/>
+      <c r="V195" s="28"/>
+      <c r="W195" s="28"/>
+      <c r="X195" s="28"/>
+      <c r="Y195" s="28"/>
+      <c r="Z195" s="29"/>
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="A196" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="D195" s="9"/>
-      <c r="E195" s="9"/>
-      <c r="F195" s="9"/>
-      <c r="G195" s="9"/>
-      <c r="H195" s="9"/>
-      <c r="I195" s="9"/>
-      <c r="J195" s="9"/>
-      <c r="K195" s="9"/>
-      <c r="L195" s="9"/>
-      <c r="M195" s="9"/>
-      <c r="N195" s="9"/>
-      <c r="O195" s="9"/>
-      <c r="P195" s="9"/>
-      <c r="Q195" s="9"/>
-      <c r="R195" s="9"/>
-      <c r="S195" s="9"/>
-      <c r="T195" s="9"/>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
-      <c r="W195" s="9"/>
-      <c r="X195" s="9"/>
-      <c r="Y195" s="9"/>
-      <c r="Z195" s="10"/>
-    </row>
-    <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="13" t="s">
+      <c r="B196" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="C196" s="1" t="s">
+      <c r="C196" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="D196" s="1"/>
-      <c r="E196" s="1"/>
-      <c r="F196" s="1"/>
-      <c r="G196" s="1"/>
-      <c r="H196" s="1"/>
-      <c r="I196" s="1"/>
-      <c r="J196" s="1"/>
-      <c r="K196" s="1"/>
-      <c r="L196" s="1"/>
-      <c r="M196" s="1"/>
-      <c r="N196" s="1"/>
-      <c r="O196" s="1"/>
-      <c r="P196" s="1"/>
-      <c r="Q196" s="1"/>
-      <c r="R196" s="1"/>
-      <c r="S196" s="1"/>
-      <c r="T196" s="1"/>
-      <c r="U196" s="1"/>
-      <c r="V196" s="1"/>
-      <c r="W196" s="1"/>
-      <c r="X196" s="1"/>
-      <c r="Y196" s="1"/>
-      <c r="Z196" s="12"/>
+      <c r="D196" s="9"/>
+      <c r="E196" s="9"/>
+      <c r="F196" s="9"/>
+      <c r="G196" s="9"/>
+      <c r="H196" s="9"/>
+      <c r="I196" s="9"/>
+      <c r="J196" s="9"/>
+      <c r="K196" s="9"/>
+      <c r="L196" s="9"/>
+      <c r="M196" s="9"/>
+      <c r="N196" s="9"/>
+      <c r="O196" s="9"/>
+      <c r="P196" s="9"/>
+      <c r="Q196" s="9"/>
+      <c r="R196" s="9"/>
+      <c r="S196" s="9"/>
+      <c r="T196" s="9"/>
+      <c r="U196" s="9"/>
+      <c r="V196" s="9"/>
+      <c r="W196" s="9"/>
+      <c r="X196" s="9"/>
+      <c r="Y196" s="9"/>
+      <c r="Z196" s="10"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="13" t="s">
         <v>341</v>
       </c>
       <c r="B197" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C197" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
@@ -8280,42 +8303,42 @@
       <c r="Z197" s="12"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="7" t="s">
+      <c r="A198" s="30" t="s">
+        <v>343</v>
+      </c>
+      <c r="B198" s="31" t="s">
+        <v>343</v>
+      </c>
+      <c r="C198" s="32" t="s">
         <v>344</v>
       </c>
-      <c r="B198" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="C198" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="D198" s="9"/>
-      <c r="E198" s="9"/>
-      <c r="F198" s="9"/>
-      <c r="G198" s="9"/>
-      <c r="H198" s="9"/>
-      <c r="I198" s="9"/>
-      <c r="J198" s="9"/>
-      <c r="K198" s="9"/>
-      <c r="L198" s="9"/>
-      <c r="M198" s="9"/>
-      <c r="N198" s="9"/>
-      <c r="O198" s="9"/>
-      <c r="P198" s="9"/>
-      <c r="Q198" s="9"/>
-      <c r="R198" s="9"/>
-      <c r="S198" s="9"/>
-      <c r="T198" s="9"/>
-      <c r="U198" s="9"/>
-      <c r="V198" s="9"/>
-      <c r="W198" s="9"/>
-      <c r="X198" s="9"/>
-      <c r="Y198" s="9"/>
-      <c r="Z198" s="10"/>
+      <c r="D198" s="1"/>
+      <c r="E198" s="1"/>
+      <c r="F198" s="1"/>
+      <c r="G198" s="1"/>
+      <c r="H198" s="1"/>
+      <c r="I198" s="1"/>
+      <c r="J198" s="1"/>
+      <c r="K198" s="1"/>
+      <c r="L198" s="1"/>
+      <c r="M198" s="1"/>
+      <c r="N198" s="1"/>
+      <c r="O198" s="1"/>
+      <c r="P198" s="1"/>
+      <c r="Q198" s="1"/>
+      <c r="R198" s="1"/>
+      <c r="S198" s="1"/>
+      <c r="T198" s="1"/>
+      <c r="U198" s="1"/>
+      <c r="V198" s="1"/>
+      <c r="W198" s="1"/>
+      <c r="X198" s="1"/>
+      <c r="Y198" s="1"/>
+      <c r="Z198" s="12"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>346</v>
@@ -8348,77 +8371,83 @@
       <c r="Z199" s="12"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="13" t="s">
+      <c r="A200" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="B200" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="C200" s="1" t="s">
+      <c r="C200" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="D200" s="1"/>
-      <c r="E200" s="1"/>
-      <c r="F200" s="1"/>
-      <c r="G200" s="1"/>
-      <c r="H200" s="1"/>
-      <c r="I200" s="1"/>
-      <c r="J200" s="1"/>
-      <c r="K200" s="1"/>
-      <c r="L200" s="1"/>
-      <c r="M200" s="1"/>
-      <c r="N200" s="1"/>
-      <c r="O200" s="1"/>
-      <c r="P200" s="1"/>
-      <c r="Q200" s="1"/>
-      <c r="R200" s="1"/>
-      <c r="S200" s="1"/>
-      <c r="T200" s="1"/>
-      <c r="U200" s="1"/>
-      <c r="V200" s="1"/>
-      <c r="W200" s="1"/>
-      <c r="X200" s="1"/>
-      <c r="Y200" s="1"/>
-      <c r="Z200" s="12"/>
+      <c r="D200" s="9"/>
+      <c r="E200" s="9"/>
+      <c r="F200" s="9"/>
+      <c r="G200" s="9"/>
+      <c r="H200" s="9"/>
+      <c r="I200" s="9"/>
+      <c r="J200" s="9"/>
+      <c r="K200" s="9"/>
+      <c r="L200" s="9"/>
+      <c r="M200" s="9"/>
+      <c r="N200" s="9"/>
+      <c r="O200" s="9"/>
+      <c r="P200" s="9"/>
+      <c r="Q200" s="9"/>
+      <c r="R200" s="9"/>
+      <c r="S200" s="9"/>
+      <c r="T200" s="9"/>
+      <c r="U200" s="9"/>
+      <c r="V200" s="9"/>
+      <c r="W200" s="9"/>
+      <c r="X200" s="9"/>
+      <c r="Y200" s="9"/>
+      <c r="Z200" s="10"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="14" t="s">
+      <c r="A201" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="B201" s="15" t="s">
+      <c r="B201" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C201" s="15" t="s">
+      <c r="C201" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="D201" s="15"/>
-      <c r="E201" s="15"/>
-      <c r="F201" s="15"/>
-      <c r="G201" s="15"/>
-      <c r="H201" s="15"/>
-      <c r="I201" s="15"/>
-      <c r="J201" s="15"/>
-      <c r="K201" s="15"/>
-      <c r="L201" s="15"/>
-      <c r="M201" s="15"/>
-      <c r="N201" s="15"/>
-      <c r="O201" s="15"/>
-      <c r="P201" s="15"/>
-      <c r="Q201" s="15"/>
-      <c r="R201" s="15"/>
-      <c r="S201" s="15"/>
-      <c r="T201" s="15"/>
-      <c r="U201" s="15"/>
-      <c r="V201" s="15"/>
-      <c r="W201" s="15"/>
-      <c r="X201" s="15"/>
-      <c r="Y201" s="15"/>
-      <c r="Z201" s="16"/>
+      <c r="D201" s="1"/>
+      <c r="E201" s="1"/>
+      <c r="F201" s="1"/>
+      <c r="G201" s="1"/>
+      <c r="H201" s="1"/>
+      <c r="I201" s="1"/>
+      <c r="J201" s="1"/>
+      <c r="K201" s="1"/>
+      <c r="L201" s="1"/>
+      <c r="M201" s="1"/>
+      <c r="N201" s="1"/>
+      <c r="O201" s="1"/>
+      <c r="P201" s="1"/>
+      <c r="Q201" s="1"/>
+      <c r="R201" s="1"/>
+      <c r="S201" s="1"/>
+      <c r="T201" s="1"/>
+      <c r="U201" s="1"/>
+      <c r="V201" s="1"/>
+      <c r="W201" s="1"/>
+      <c r="X201" s="1"/>
+      <c r="Y201" s="1"/>
+      <c r="Z201" s="12"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="1"/>
-      <c r="B202" s="1"/>
-      <c r="C202" s="1"/>
+      <c r="A202" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>353</v>
+      </c>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
@@ -8441,48 +8470,46 @@
       <c r="W202" s="1"/>
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
-      <c r="Z202" s="1"/>
+      <c r="Z202" s="12"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="B203" s="2"/>
-      <c r="C203" s="2"/>
-      <c r="D203" s="2"/>
-      <c r="E203" s="2"/>
-      <c r="F203" s="2"/>
-      <c r="G203" s="2"/>
-      <c r="H203" s="2"/>
-      <c r="I203" s="2"/>
-      <c r="J203" s="2"/>
-      <c r="K203" s="2"/>
-      <c r="L203" s="2"/>
-      <c r="M203" s="2"/>
-      <c r="N203" s="2"/>
-      <c r="O203" s="2"/>
-      <c r="P203" s="2"/>
-      <c r="Q203" s="2"/>
-      <c r="R203" s="2"/>
-      <c r="S203" s="2"/>
-      <c r="T203" s="2"/>
-      <c r="U203" s="2"/>
-      <c r="V203" s="2"/>
-      <c r="W203" s="2"/>
-      <c r="X203" s="2"/>
-      <c r="Y203" s="2"/>
-      <c r="Z203" s="2"/>
+      <c r="A203" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="B203" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="C203" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="D203" s="15"/>
+      <c r="E203" s="15"/>
+      <c r="F203" s="15"/>
+      <c r="G203" s="15"/>
+      <c r="H203" s="15"/>
+      <c r="I203" s="15"/>
+      <c r="J203" s="15"/>
+      <c r="K203" s="15"/>
+      <c r="L203" s="15"/>
+      <c r="M203" s="15"/>
+      <c r="N203" s="15"/>
+      <c r="O203" s="15"/>
+      <c r="P203" s="15"/>
+      <c r="Q203" s="15"/>
+      <c r="R203" s="15"/>
+      <c r="S203" s="15"/>
+      <c r="T203" s="15"/>
+      <c r="U203" s="15"/>
+      <c r="V203" s="15"/>
+      <c r="W203" s="15"/>
+      <c r="X203" s="15"/>
+      <c r="Y203" s="15"/>
+      <c r="Z203" s="16"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>354</v>
-      </c>
+      <c r="A204" s="1"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
@@ -8508,38 +8535,34 @@
       <c r="Z204" s="1"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C205" s="1" t="s">
+      <c r="A205" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D205" s="1"/>
-      <c r="E205" s="1"/>
-      <c r="F205" s="1"/>
-      <c r="G205" s="1"/>
-      <c r="H205" s="1"/>
-      <c r="I205" s="1"/>
-      <c r="J205" s="1"/>
-      <c r="K205" s="1"/>
-      <c r="L205" s="1"/>
-      <c r="M205" s="1"/>
-      <c r="N205" s="1"/>
-      <c r="O205" s="1"/>
-      <c r="P205" s="1"/>
-      <c r="Q205" s="1"/>
-      <c r="R205" s="1"/>
-      <c r="S205" s="1"/>
-      <c r="T205" s="1"/>
-      <c r="U205" s="1"/>
-      <c r="V205" s="1"/>
-      <c r="W205" s="1"/>
-      <c r="X205" s="1"/>
-      <c r="Y205" s="1"/>
-      <c r="Z205" s="1"/>
+      <c r="B205" s="2"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
+      <c r="E205" s="2"/>
+      <c r="F205" s="2"/>
+      <c r="G205" s="2"/>
+      <c r="H205" s="2"/>
+      <c r="I205" s="2"/>
+      <c r="J205" s="2"/>
+      <c r="K205" s="2"/>
+      <c r="L205" s="2"/>
+      <c r="M205" s="2"/>
+      <c r="N205" s="2"/>
+      <c r="O205" s="2"/>
+      <c r="P205" s="2"/>
+      <c r="Q205" s="2"/>
+      <c r="R205" s="2"/>
+      <c r="S205" s="2"/>
+      <c r="T205" s="2"/>
+      <c r="U205" s="2"/>
+      <c r="V205" s="2"/>
+      <c r="W205" s="2"/>
+      <c r="X205" s="2"/>
+      <c r="Y205" s="2"/>
+      <c r="Z205" s="2"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="1" t="s">
@@ -8610,13 +8633,13 @@
       <c r="Z207" s="1"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="29" t="s">
+      <c r="A208" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B208" s="20" t="s">
+      <c r="B208" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C208" s="29" t="s">
+      <c r="C208" s="1" t="s">
         <v>362</v>
       </c>
       <c r="D208" s="1"/>
@@ -8644,9 +8667,15 @@
       <c r="Z208" s="1"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="1"/>
-      <c r="B209" s="1"/>
-      <c r="C209" s="1"/>
+      <c r="A209" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>364</v>
+      </c>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
@@ -8672,45 +8701,43 @@
       <c r="Z209" s="1"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B210" s="2"/>
-      <c r="C210" s="2"/>
-      <c r="D210" s="2"/>
-      <c r="E210" s="2"/>
-      <c r="F210" s="2"/>
-      <c r="G210" s="2"/>
-      <c r="H210" s="2"/>
-      <c r="I210" s="2"/>
-      <c r="J210" s="2"/>
-      <c r="K210" s="2"/>
-      <c r="L210" s="2"/>
-      <c r="M210" s="2"/>
-      <c r="N210" s="2"/>
-      <c r="O210" s="2"/>
-      <c r="P210" s="2"/>
-      <c r="Q210" s="2"/>
-      <c r="R210" s="2"/>
-      <c r="S210" s="2"/>
-      <c r="T210" s="2"/>
-      <c r="U210" s="2"/>
-      <c r="V210" s="2"/>
-      <c r="W210" s="2"/>
-      <c r="X210" s="2"/>
-      <c r="Y210" s="2"/>
-      <c r="Z210" s="2"/>
+      <c r="A210" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B210" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D210" s="1"/>
+      <c r="E210" s="1"/>
+      <c r="F210" s="1"/>
+      <c r="G210" s="1"/>
+      <c r="H210" s="1"/>
+      <c r="I210" s="1"/>
+      <c r="J210" s="1"/>
+      <c r="K210" s="1"/>
+      <c r="L210" s="1"/>
+      <c r="M210" s="1"/>
+      <c r="N210" s="1"/>
+      <c r="O210" s="1"/>
+      <c r="P210" s="1"/>
+      <c r="Q210" s="1"/>
+      <c r="R210" s="1"/>
+      <c r="S210" s="1"/>
+      <c r="T210" s="1"/>
+      <c r="U210" s="1"/>
+      <c r="V210" s="1"/>
+      <c r="W210" s="1"/>
+      <c r="X210" s="1"/>
+      <c r="Y210" s="1"/>
+      <c r="Z210" s="1"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>365</v>
-      </c>
+      <c r="A211" s="1"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
@@ -8736,73 +8763,73 @@
       <c r="Z211" s="1"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="1"/>
-      <c r="B212" s="1"/>
-      <c r="C212" s="1"/>
-      <c r="D212" s="1"/>
-      <c r="E212" s="1"/>
-      <c r="F212" s="1"/>
-      <c r="G212" s="1"/>
-      <c r="H212" s="1"/>
-      <c r="I212" s="1"/>
-      <c r="J212" s="1"/>
-      <c r="K212" s="1"/>
-      <c r="L212" s="1"/>
-      <c r="M212" s="1"/>
-      <c r="N212" s="1"/>
-      <c r="O212" s="1"/>
-      <c r="P212" s="1"/>
-      <c r="Q212" s="1"/>
-      <c r="R212" s="1"/>
-      <c r="S212" s="1"/>
-      <c r="T212" s="1"/>
-      <c r="U212" s="1"/>
-      <c r="V212" s="1"/>
-      <c r="W212" s="1"/>
-      <c r="X212" s="1"/>
-      <c r="Y212" s="1"/>
-      <c r="Z212" s="1"/>
+      <c r="A212" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B212" s="2"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
+      <c r="E212" s="2"/>
+      <c r="F212" s="2"/>
+      <c r="G212" s="2"/>
+      <c r="H212" s="2"/>
+      <c r="I212" s="2"/>
+      <c r="J212" s="2"/>
+      <c r="K212" s="2"/>
+      <c r="L212" s="2"/>
+      <c r="M212" s="2"/>
+      <c r="N212" s="2"/>
+      <c r="O212" s="2"/>
+      <c r="P212" s="2"/>
+      <c r="Q212" s="2"/>
+      <c r="R212" s="2"/>
+      <c r="S212" s="2"/>
+      <c r="T212" s="2"/>
+      <c r="U212" s="2"/>
+      <c r="V212" s="2"/>
+      <c r="W212" s="2"/>
+      <c r="X212" s="2"/>
+      <c r="Y212" s="2"/>
+      <c r="Z212" s="2"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B213" s="2"/>
-      <c r="C213" s="2"/>
-      <c r="D213" s="2"/>
-      <c r="E213" s="2"/>
-      <c r="F213" s="2"/>
-      <c r="G213" s="2"/>
-      <c r="H213" s="2"/>
-      <c r="I213" s="2"/>
-      <c r="J213" s="2"/>
-      <c r="K213" s="2"/>
-      <c r="L213" s="2"/>
-      <c r="M213" s="2"/>
-      <c r="N213" s="2"/>
-      <c r="O213" s="2"/>
-      <c r="P213" s="2"/>
-      <c r="Q213" s="2"/>
-      <c r="R213" s="2"/>
-      <c r="S213" s="2"/>
-      <c r="T213" s="2"/>
-      <c r="U213" s="2"/>
-      <c r="V213" s="2"/>
-      <c r="W213" s="2"/>
-      <c r="X213" s="2"/>
-      <c r="Y213" s="2"/>
-      <c r="Z213" s="2"/>
+      <c r="A213" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D213" s="1"/>
+      <c r="E213" s="1"/>
+      <c r="F213" s="1"/>
+      <c r="G213" s="1"/>
+      <c r="H213" s="1"/>
+      <c r="I213" s="1"/>
+      <c r="J213" s="1"/>
+      <c r="K213" s="1"/>
+      <c r="L213" s="1"/>
+      <c r="M213" s="1"/>
+      <c r="N213" s="1"/>
+      <c r="O213" s="1"/>
+      <c r="P213" s="1"/>
+      <c r="Q213" s="1"/>
+      <c r="R213" s="1"/>
+      <c r="S213" s="1"/>
+      <c r="T213" s="1"/>
+      <c r="U213" s="1"/>
+      <c r="V213" s="1"/>
+      <c r="W213" s="1"/>
+      <c r="X213" s="1"/>
+      <c r="Y213" s="1"/>
+      <c r="Z213" s="1"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="A214" s="1"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
@@ -8828,48 +8855,44 @@
       <c r="Z214" s="1"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="1" t="s">
+      <c r="A215" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="D215" s="1"/>
-      <c r="E215" s="1"/>
-      <c r="F215" s="1"/>
-      <c r="G215" s="1"/>
-      <c r="H215" s="1"/>
-      <c r="I215" s="1"/>
-      <c r="J215" s="1"/>
-      <c r="K215" s="1"/>
-      <c r="L215" s="1"/>
-      <c r="M215" s="1"/>
-      <c r="N215" s="1"/>
-      <c r="O215" s="1"/>
-      <c r="P215" s="1"/>
-      <c r="Q215" s="1"/>
-      <c r="R215" s="1"/>
-      <c r="S215" s="1"/>
-      <c r="T215" s="1"/>
-      <c r="U215" s="1"/>
-      <c r="V215" s="1"/>
-      <c r="W215" s="1"/>
-      <c r="X215" s="1"/>
-      <c r="Y215" s="1"/>
-      <c r="Z215" s="1"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+      <c r="E215" s="2"/>
+      <c r="F215" s="2"/>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
+      <c r="J215" s="2"/>
+      <c r="K215" s="2"/>
+      <c r="L215" s="2"/>
+      <c r="M215" s="2"/>
+      <c r="N215" s="2"/>
+      <c r="O215" s="2"/>
+      <c r="P215" s="2"/>
+      <c r="Q215" s="2"/>
+      <c r="R215" s="2"/>
+      <c r="S215" s="2"/>
+      <c r="T215" s="2"/>
+      <c r="U215" s="2"/>
+      <c r="V215" s="2"/>
+      <c r="W215" s="2"/>
+      <c r="X215" s="2"/>
+      <c r="Y215" s="2"/>
+      <c r="Z215" s="2"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -8897,13 +8920,13 @@
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C217" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
@@ -8931,13 +8954,13 @@
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C218" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="C218" s="1" t="s">
-        <v>380</v>
       </c>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
@@ -8965,7 +8988,7 @@
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>381</v>
@@ -9002,10 +9025,10 @@
         <v>383</v>
       </c>
       <c r="B220" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C220" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="C220" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
@@ -9033,13 +9056,13 @@
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C221" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
@@ -9067,13 +9090,13 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C222" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
@@ -9101,13 +9124,13 @@
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C223" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>394</v>
       </c>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
@@ -9134,9 +9157,15 @@
       <c r="Z223" s="1"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="1"/>
-      <c r="B224" s="1"/>
-      <c r="C224" s="1"/>
+      <c r="A224" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>395</v>
+      </c>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
@@ -9162,45 +9191,43 @@
       <c r="Z224" s="1"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B225" s="2"/>
-      <c r="C225" s="2"/>
-      <c r="D225" s="2"/>
-      <c r="E225" s="2"/>
-      <c r="F225" s="2"/>
-      <c r="G225" s="2"/>
-      <c r="H225" s="2"/>
-      <c r="I225" s="2"/>
-      <c r="J225" s="2"/>
-      <c r="K225" s="2"/>
-      <c r="L225" s="2"/>
-      <c r="M225" s="2"/>
-      <c r="N225" s="2"/>
-      <c r="O225" s="2"/>
-      <c r="P225" s="2"/>
-      <c r="Q225" s="2"/>
-      <c r="R225" s="2"/>
-      <c r="S225" s="2"/>
-      <c r="T225" s="2"/>
-      <c r="U225" s="2"/>
-      <c r="V225" s="2"/>
-      <c r="W225" s="2"/>
-      <c r="X225" s="2"/>
-      <c r="Y225" s="2"/>
-      <c r="Z225" s="2"/>
+      <c r="A225" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D225" s="1"/>
+      <c r="E225" s="1"/>
+      <c r="F225" s="1"/>
+      <c r="G225" s="1"/>
+      <c r="H225" s="1"/>
+      <c r="I225" s="1"/>
+      <c r="J225" s="1"/>
+      <c r="K225" s="1"/>
+      <c r="L225" s="1"/>
+      <c r="M225" s="1"/>
+      <c r="N225" s="1"/>
+      <c r="O225" s="1"/>
+      <c r="P225" s="1"/>
+      <c r="Q225" s="1"/>
+      <c r="R225" s="1"/>
+      <c r="S225" s="1"/>
+      <c r="T225" s="1"/>
+      <c r="U225" s="1"/>
+      <c r="V225" s="1"/>
+      <c r="W225" s="1"/>
+      <c r="X225" s="1"/>
+      <c r="Y225" s="1"/>
+      <c r="Z225" s="1"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="A226" s="1"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="1"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
@@ -9226,48 +9253,44 @@
       <c r="Z226" s="1"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D227" s="1"/>
-      <c r="E227" s="1"/>
-      <c r="F227" s="1"/>
-      <c r="G227" s="1"/>
-      <c r="H227" s="1"/>
-      <c r="I227" s="1"/>
-      <c r="J227" s="1"/>
-      <c r="K227" s="1"/>
-      <c r="L227" s="1"/>
-      <c r="M227" s="1"/>
-      <c r="N227" s="1"/>
-      <c r="O227" s="1"/>
-      <c r="P227" s="1"/>
-      <c r="Q227" s="1"/>
-      <c r="R227" s="1"/>
-      <c r="S227" s="1"/>
-      <c r="T227" s="1"/>
-      <c r="U227" s="1"/>
-      <c r="V227" s="1"/>
-      <c r="W227" s="1"/>
-      <c r="X227" s="1"/>
-      <c r="Y227" s="1"/>
-      <c r="Z227" s="1"/>
+      <c r="A227" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B227" s="2"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
+      <c r="E227" s="2"/>
+      <c r="F227" s="2"/>
+      <c r="G227" s="2"/>
+      <c r="H227" s="2"/>
+      <c r="I227" s="2"/>
+      <c r="J227" s="2"/>
+      <c r="K227" s="2"/>
+      <c r="L227" s="2"/>
+      <c r="M227" s="2"/>
+      <c r="N227" s="2"/>
+      <c r="O227" s="2"/>
+      <c r="P227" s="2"/>
+      <c r="Q227" s="2"/>
+      <c r="R227" s="2"/>
+      <c r="S227" s="2"/>
+      <c r="T227" s="2"/>
+      <c r="U227" s="2"/>
+      <c r="V227" s="2"/>
+      <c r="W227" s="2"/>
+      <c r="X227" s="2"/>
+      <c r="Y227" s="2"/>
+      <c r="Z227" s="2"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
@@ -9295,13 +9318,13 @@
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>400</v>
+        <v>71</v>
       </c>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
@@ -9329,13 +9352,13 @@
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>402</v>
+        <v>71</v>
       </c>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
@@ -9403,7 +9426,7 @@
         <v>405</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>20</v>
+        <v>406</v>
       </c>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
@@ -9431,13 +9454,13 @@
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>16</v>
+        <v>408</v>
       </c>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
@@ -9465,13 +9488,13 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
@@ -9499,13 +9522,13 @@
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>410</v>
+        <v>16</v>
       </c>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
@@ -9536,10 +9559,10 @@
         <v>411</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>413</v>
+        <v>18</v>
       </c>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
@@ -9567,13 +9590,13 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C237" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="B237" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
@@ -9600,9 +9623,15 @@
       <c r="Z237" s="1"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="1"/>
-      <c r="B238" s="1"/>
-      <c r="C238" s="1"/>
+      <c r="A238" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>417</v>
+      </c>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
@@ -9628,9 +9657,15 @@
       <c r="Z238" s="1"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="1"/>
-      <c r="B239" s="1"/>
-      <c r="C239" s="1"/>
+      <c r="A239" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>420</v>
+      </c>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
@@ -15200,60 +15235,60 @@
       <c r="Z437" s="1"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="17"/>
-      <c r="B438" s="17"/>
-      <c r="C438" s="17"/>
-      <c r="D438" s="17"/>
-      <c r="E438" s="17"/>
-      <c r="F438" s="17"/>
-      <c r="G438" s="17"/>
-      <c r="H438" s="17"/>
-      <c r="I438" s="17"/>
-      <c r="J438" s="17"/>
-      <c r="K438" s="17"/>
-      <c r="L438" s="17"/>
-      <c r="M438" s="17"/>
-      <c r="N438" s="17"/>
-      <c r="O438" s="17"/>
-      <c r="P438" s="17"/>
-      <c r="Q438" s="17"/>
-      <c r="R438" s="17"/>
-      <c r="S438" s="17"/>
-      <c r="T438" s="17"/>
-      <c r="U438" s="17"/>
-      <c r="V438" s="17"/>
-      <c r="W438" s="17"/>
-      <c r="X438" s="17"/>
-      <c r="Y438" s="17"/>
-      <c r="Z438" s="17"/>
+      <c r="A438" s="1"/>
+      <c r="B438" s="1"/>
+      <c r="C438" s="1"/>
+      <c r="D438" s="1"/>
+      <c r="E438" s="1"/>
+      <c r="F438" s="1"/>
+      <c r="G438" s="1"/>
+      <c r="H438" s="1"/>
+      <c r="I438" s="1"/>
+      <c r="J438" s="1"/>
+      <c r="K438" s="1"/>
+      <c r="L438" s="1"/>
+      <c r="M438" s="1"/>
+      <c r="N438" s="1"/>
+      <c r="O438" s="1"/>
+      <c r="P438" s="1"/>
+      <c r="Q438" s="1"/>
+      <c r="R438" s="1"/>
+      <c r="S438" s="1"/>
+      <c r="T438" s="1"/>
+      <c r="U438" s="1"/>
+      <c r="V438" s="1"/>
+      <c r="W438" s="1"/>
+      <c r="X438" s="1"/>
+      <c r="Y438" s="1"/>
+      <c r="Z438" s="1"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="17"/>
-      <c r="B439" s="17"/>
-      <c r="C439" s="17"/>
-      <c r="D439" s="17"/>
-      <c r="E439" s="17"/>
-      <c r="F439" s="17"/>
-      <c r="G439" s="17"/>
-      <c r="H439" s="17"/>
-      <c r="I439" s="17"/>
-      <c r="J439" s="17"/>
-      <c r="K439" s="17"/>
-      <c r="L439" s="17"/>
-      <c r="M439" s="17"/>
-      <c r="N439" s="17"/>
-      <c r="O439" s="17"/>
-      <c r="P439" s="17"/>
-      <c r="Q439" s="17"/>
-      <c r="R439" s="17"/>
-      <c r="S439" s="17"/>
-      <c r="T439" s="17"/>
-      <c r="U439" s="17"/>
-      <c r="V439" s="17"/>
-      <c r="W439" s="17"/>
-      <c r="X439" s="17"/>
-      <c r="Y439" s="17"/>
-      <c r="Z439" s="17"/>
+      <c r="A439" s="1"/>
+      <c r="B439" s="1"/>
+      <c r="C439" s="1"/>
+      <c r="D439" s="1"/>
+      <c r="E439" s="1"/>
+      <c r="F439" s="1"/>
+      <c r="G439" s="1"/>
+      <c r="H439" s="1"/>
+      <c r="I439" s="1"/>
+      <c r="J439" s="1"/>
+      <c r="K439" s="1"/>
+      <c r="L439" s="1"/>
+      <c r="M439" s="1"/>
+      <c r="N439" s="1"/>
+      <c r="O439" s="1"/>
+      <c r="P439" s="1"/>
+      <c r="Q439" s="1"/>
+      <c r="R439" s="1"/>
+      <c r="S439" s="1"/>
+      <c r="T439" s="1"/>
+      <c r="U439" s="1"/>
+      <c r="V439" s="1"/>
+      <c r="W439" s="1"/>
+      <c r="X439" s="1"/>
+      <c r="Y439" s="1"/>
+      <c r="Z439" s="1"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="17"/>
@@ -31887,6 +31922,62 @@
       <c r="Y1033" s="17"/>
       <c r="Z1033" s="17"/>
     </row>
+    <row r="1034" ht="15.75" customHeight="1">
+      <c r="A1034" s="17"/>
+      <c r="B1034" s="17"/>
+      <c r="C1034" s="17"/>
+      <c r="D1034" s="17"/>
+      <c r="E1034" s="17"/>
+      <c r="F1034" s="17"/>
+      <c r="G1034" s="17"/>
+      <c r="H1034" s="17"/>
+      <c r="I1034" s="17"/>
+      <c r="J1034" s="17"/>
+      <c r="K1034" s="17"/>
+      <c r="L1034" s="17"/>
+      <c r="M1034" s="17"/>
+      <c r="N1034" s="17"/>
+      <c r="O1034" s="17"/>
+      <c r="P1034" s="17"/>
+      <c r="Q1034" s="17"/>
+      <c r="R1034" s="17"/>
+      <c r="S1034" s="17"/>
+      <c r="T1034" s="17"/>
+      <c r="U1034" s="17"/>
+      <c r="V1034" s="17"/>
+      <c r="W1034" s="17"/>
+      <c r="X1034" s="17"/>
+      <c r="Y1034" s="17"/>
+      <c r="Z1034" s="17"/>
+    </row>
+    <row r="1035" ht="15.75" customHeight="1">
+      <c r="A1035" s="17"/>
+      <c r="B1035" s="17"/>
+      <c r="C1035" s="17"/>
+      <c r="D1035" s="17"/>
+      <c r="E1035" s="17"/>
+      <c r="F1035" s="17"/>
+      <c r="G1035" s="17"/>
+      <c r="H1035" s="17"/>
+      <c r="I1035" s="17"/>
+      <c r="J1035" s="17"/>
+      <c r="K1035" s="17"/>
+      <c r="L1035" s="17"/>
+      <c r="M1035" s="17"/>
+      <c r="N1035" s="17"/>
+      <c r="O1035" s="17"/>
+      <c r="P1035" s="17"/>
+      <c r="Q1035" s="17"/>
+      <c r="R1035" s="17"/>
+      <c r="S1035" s="17"/>
+      <c r="T1035" s="17"/>
+      <c r="U1035" s="17"/>
+      <c r="V1035" s="17"/>
+      <c r="W1035" s="17"/>
+      <c r="X1035" s="17"/>
+      <c r="Y1035" s="17"/>
+      <c r="Z1035" s="17"/>
+    </row>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
